--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\TaikoNavigation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67FA74AA-6279-4269-8786-0CC6231D0DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{179B41B3-0B49-468D-BF6A-A7DC98C2788D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8352" yWindow="2664" windowWidth="20460" windowHeight="14592" xr2:uid="{21938866-CF94-43A1-8F72-DCC95449F496}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{21938866-CF94-43A1-8F72-DCC95449F496}"/>
   </bookViews>
   <sheets>
     <sheet name="deepseek_csv_20260722_b23856" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="145">
   <si>
     <t>name</t>
   </si>
@@ -474,6 +474,14 @@
   </si>
   <si>
     <t>国内玩家开发的成绩评分系统及谱面查询</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>可可子</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://kkz.haxif.com/</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1443,7 +1451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2205B9E-1FE6-4EB7-B604-2CFC0207A242}">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.5546875" customWidth="1"/>
@@ -1922,27 +1930,27 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B31" t="s">
-        <v>73</v>
+        <v>143</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="D31" t="s">
-        <v>74</v>
+        <v>139</v>
       </c>
       <c r="E31">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D32" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E32">
         <v>6</v>
@@ -1950,13 +1958,13 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D33" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E33">
         <v>6</v>
@@ -1964,13 +1972,13 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>138</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>137</v>
+        <v>78</v>
+      </c>
+      <c r="B34" t="s">
+        <v>79</v>
       </c>
       <c r="D34" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E34">
         <v>6</v>
@@ -1978,13 +1986,13 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>81</v>
-      </c>
-      <c r="B35" t="s">
-        <v>82</v>
+        <v>138</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>137</v>
       </c>
       <c r="D35" t="s">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="E35">
         <v>6</v>
@@ -1992,13 +2000,13 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B36" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D36" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E36">
         <v>6</v>
@@ -2006,13 +2014,13 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B37" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D37" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E37">
         <v>6</v>
@@ -2020,13 +2028,13 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B38" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D38" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E38">
         <v>6</v>
@@ -2034,13 +2042,13 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B39" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D39" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E39">
         <v>6</v>
@@ -2048,13 +2056,13 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B40" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D40" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E40">
         <v>6</v>
@@ -2062,13 +2070,13 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B41" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D41" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E41">
         <v>6</v>
@@ -2076,13 +2084,13 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B42" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D42" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E42">
         <v>6</v>
@@ -2090,13 +2098,13 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B43" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D43" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E43">
         <v>6</v>
@@ -2104,13 +2112,13 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B44" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D44" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E44">
         <v>6</v>
@@ -2118,16 +2126,13 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B45" t="s">
-        <v>112</v>
-      </c>
-      <c r="C45" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D45" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E45">
         <v>6</v>
@@ -2135,18 +2140,35 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>111</v>
+      </c>
+      <c r="B46" t="s">
+        <v>112</v>
+      </c>
+      <c r="C46" t="s">
+        <v>128</v>
+      </c>
+      <c r="D46" t="s">
+        <v>113</v>
+      </c>
+      <c r="E46">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>114</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B47" t="s">
         <v>115</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C47" t="s">
         <v>127</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D47" t="s">
         <v>116</v>
       </c>
-      <c r="E46">
+      <c r="E47">
         <v>6</v>
       </c>
     </row>
@@ -2156,8 +2178,9 @@
     <hyperlink ref="B24" r:id="rId1" xr:uid="{0814D534-9BBD-4FF2-91BF-D9D2FA195367}"/>
     <hyperlink ref="B26" r:id="rId2" xr:uid="{1C29CD7D-8195-4F43-BF25-3937379C553D}"/>
     <hyperlink ref="B25" r:id="rId3" xr:uid="{C7DC1DD1-A540-4732-A529-6E4F4FC7E8F3}"/>
-    <hyperlink ref="B34" r:id="rId4" xr:uid="{CACBC6E3-169E-4706-B683-51554D0D68AD}"/>
+    <hyperlink ref="B35" r:id="rId4" xr:uid="{CACBC6E3-169E-4706-B683-51554D0D68AD}"/>
     <hyperlink ref="B10" r:id="rId5" xr:uid="{E4702D2D-6FCD-4B5B-9E81-602FCFEC045E}"/>
+    <hyperlink ref="B31" r:id="rId6" xr:uid="{A1F7C2BA-EE73-4EAF-99B5-5E02AFC9E006}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{179B41B3-0B49-468D-BF6A-A7DC98C2788D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B511739D-B248-4126-BD16-58E6164312D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{21938866-CF94-43A1-8F72-DCC95449F496}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="153">
   <si>
     <t>name</t>
   </si>
@@ -115,373 +115,431 @@
     <t>DonderNote.png</t>
   </si>
   <si>
+    <t>OpenTaiko</t>
+  </si>
+  <si>
+    <t>https://opentaiko.github.io/</t>
+  </si>
+  <si>
+    <t>OpenTaiko.ico</t>
+  </si>
+  <si>
+    <t>ESE TJA</t>
+  </si>
+  <si>
+    <t>https://ese.tjadataba.se/ESE/ESE/</t>
+  </si>
+  <si>
+    <t>ese.png</t>
+  </si>
+  <si>
+    <t>ESE Helper</t>
+  </si>
+  <si>
+    <t>https://taiko.vanillaaaa.org/</t>
+  </si>
+  <si>
+    <t>https://wwaya.lanzoup.com/iHj8b3e7ooyh</t>
+  </si>
+  <si>
+    <t>可视化的谱面编辑，让小白也能迅速创建自己的太鼓谱面</t>
+  </si>
+  <si>
+    <t>PeepoDrumKit.ico</t>
+  </si>
+  <si>
+    <t>TaikoWeb</t>
+  </si>
+  <si>
+    <t>https://taiko.asia/</t>
+  </si>
+  <si>
+    <t>太鼓达人在线模拟器</t>
+  </si>
+  <si>
+    <t>taikoweb.png</t>
+  </si>
+  <si>
+    <t>歌曲检索器</t>
+  </si>
+  <si>
+    <t>https://olaf5103.cn:765/taiko/songs</t>
+  </si>
+  <si>
+    <t>Donder Asistant</t>
+  </si>
+  <si>
+    <t>https://dafrok.github.io/donder-assistant/analysis</t>
+  </si>
+  <si>
+    <t>Tja-Tools</t>
+  </si>
+  <si>
+    <t>可以将tja文件转化为静态谱面图</t>
+  </si>
+  <si>
+    <t>Tja Analyser</t>
+  </si>
+  <si>
+    <t>TaikoImager</t>
+  </si>
+  <si>
+    <t>可以获得还原官方视觉效果的谱面片段或谱面图，支持各种演奏选项</t>
+  </si>
+  <si>
+    <t>AI定数预测</t>
+  </si>
+  <si>
+    <t>让AI对你创作的谱面进行难度的初步评估</t>
+  </si>
+  <si>
+    <t>kokoko.jpg</t>
+  </si>
+  <si>
+    <t>菌菌控制台</t>
+  </si>
+  <si>
+    <t>https://kinoko.zorua.cn/</t>
+  </si>
+  <si>
+    <t>菌菌控制台！可以管理自己的成绩以及使用菌菌的多项隐藏功能！</t>
+  </si>
+  <si>
+    <t>junjun.png</t>
+  </si>
+  <si>
+    <t>菌菌别名表格</t>
+  </si>
+  <si>
+    <t>https://www.kdocs.cn/l/cauSVZId2ohu</t>
+  </si>
+  <si>
+    <t>Sakura Bot</t>
+  </si>
+  <si>
+    <t>https://viewer.sakura-bot.cn/</t>
+  </si>
+  <si>
+    <t>猫鼓的小店</t>
+  </si>
+  <si>
+    <t>cat.png</t>
+  </si>
+  <si>
+    <t>power.png</t>
+  </si>
+  <si>
+    <t>sakataiko.png</t>
+  </si>
+  <si>
+    <t>stg.png</t>
+  </si>
+  <si>
+    <t>伪都特产私棍</t>
+  </si>
+  <si>
+    <t>otto.png</t>
+  </si>
+  <si>
+    <t>单手全连逆战</t>
+  </si>
+  <si>
+    <t>nizhan.png</t>
+  </si>
+  <si>
+    <t>狂澜怒涛</t>
+  </si>
+  <si>
+    <t>7f7f.png</t>
+  </si>
+  <si>
+    <t>watermelon.png</t>
+  </si>
+  <si>
+    <t>ZDR</t>
+  </si>
+  <si>
+    <t>zdr.png</t>
+  </si>
+  <si>
+    <t>活体搁浅</t>
+  </si>
+  <si>
+    <t>wai.jpg</t>
+  </si>
+  <si>
+    <t>deng.png</t>
+  </si>
+  <si>
+    <t>小言罐头</t>
+  </si>
+  <si>
+    <t>yan.png</t>
+  </si>
+  <si>
+    <t>yuan.png</t>
+  </si>
+  <si>
+    <t>小章木工坊</t>
+  </si>
+  <si>
+    <t>https://mobile.yangkeduo.com/mall_page.html?ps=IpGOWhdEwr</t>
+  </si>
+  <si>
+    <t>pdd.png</t>
+  </si>
+  <si>
+    <t>铭盛科技</t>
+  </si>
+  <si>
+    <t>mingsheng.png</t>
+  </si>
+  <si>
+    <t>太鼓之达人官方</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>太鼓之达人官方Bilibili账号</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>华立电竞官方Bilibili账号</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>太鼓Fandom</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>全国玩家群</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>全国范围的2000人玩家交流群</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>太鼓WIKI 日</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>太鼓WIKI 韩</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PeepoDrumKit</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Database定数</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>华立官方淘汰的次品官机配件，可以尝试抽奖</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>20元以内性价比首选，建议选圆头枫木，自己购置手胶</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>为歌曲添加别名用于菌菌的歌曲查询</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://imager.donders.work</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://rating.haxif.com</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI Rating分析</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>让AI对你的成绩信息进行分析总结</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>stv.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>控制器调试辅助</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>StevenXMH</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>kokoko.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://wiki.ourtaiko.org/songs</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OurtaikoWiki</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>国内玩家开发的成绩评分系统及谱面查询</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>可可子</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://kkz.haxif.com/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://shop525820965.taobao.com/category.htm?spm=pc_detail.30350276.shop_block.dshopinfo.56be7dd6dsI5yg&amp;topIds=719510077825</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Power的小店</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://shop104239116.taobao.com/category.htm?spm=pc_detail.30350276.shop_block.dshopinfo.6d1c6252j87z2N&amp;topIds=1050934996989</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>鱼鼓的小店</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.bought.0.0.5228252dPRFudb&amp;userId=3698605461</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.bought.0.0.5228252dPRFudb&amp;userId=1107549877</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>神童同学</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.27bd42b3JlfOmI&amp;userId=2709663921</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.6ad31a5as9AFCH&amp;userId=2213174146625</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>西瓜的音游小铺</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.12cf163dmL6Yrg&amp;userId=2135576311</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.46e4b2f2l91x1H&amp;userId=674644841</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://shop109402001.taobao.com/category.htm?spm=pc_detail.30350276.shop_block.dshopinfo.32217dd6Wwfp8W&amp;topIds=567063533860</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.52ca49fauX932Z&amp;userId=3704968269</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.19c73350BIZScL&amp;userId=3887875950</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>不灭的灯</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>哈基缘</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.150a505eFDpfwo&amp;userId=45429781</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.7dc67a0caZ3ysg&amp;userId=2200623233408</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.5b1052c7F1Fyox&amp;userId=2215320654516</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://e.tb.cn/h.8XcgB01nntTZ3dL?tk=AyHygHkEYP4</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TjaVideoPlayer</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://video.donders.work</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>将tja文件渲染为视频，便于分享</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>TaikoNauts</t>
-  </si>
-  <si>
-    <t>https://seesaawiki.jp/taikonauts/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tjaanalyzer-ja.ckq.me</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://whmhammer.github.io/tja-tools</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://stevetaikocon.stevexmh.net</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tjapre.haxif.com</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>TaikoNauts.ico</t>
-  </si>
-  <si>
-    <t>OpenTaiko</t>
-  </si>
-  <si>
-    <t>https://opentaiko.github.io/</t>
-  </si>
-  <si>
-    <t>OpenTaiko.ico</t>
-  </si>
-  <si>
-    <t>ESE TJA</t>
-  </si>
-  <si>
-    <t>https://ese.tjadataba.se/ESE/ESE/</t>
-  </si>
-  <si>
-    <t>ese.png</t>
-  </si>
-  <si>
-    <t>ESE Helper</t>
-  </si>
-  <si>
-    <t>https://taiko.vanillaaaa.org/</t>
-  </si>
-  <si>
-    <t>https://wwaya.lanzoup.com/iHj8b3e7ooyh</t>
-  </si>
-  <si>
-    <t>可视化的谱面编辑，让小白也能迅速创建自己的太鼓谱面</t>
-  </si>
-  <si>
-    <t>PeepoDrumKit.ico</t>
-  </si>
-  <si>
-    <t>TaikoWeb</t>
-  </si>
-  <si>
-    <t>https://taiko.asia/</t>
-  </si>
-  <si>
-    <t>太鼓达人在线模拟器</t>
-  </si>
-  <si>
-    <t>taikoweb.png</t>
-  </si>
-  <si>
-    <t>歌曲检索器</t>
-  </si>
-  <si>
-    <t>https://olaf5103.cn:765/taiko/songs</t>
-  </si>
-  <si>
-    <t>Donder Asistant</t>
-  </si>
-  <si>
-    <t>https://dafrok.github.io/donder-assistant/analysis</t>
-  </si>
-  <si>
-    <t>Tja-Tools</t>
-  </si>
-  <si>
-    <t>https://whmhammer.github.io/tja-tools/</t>
-  </si>
-  <si>
-    <t>可以将tja文件转化为静态谱面图</t>
-  </si>
-  <si>
-    <t>Tja Analyser</t>
-  </si>
-  <si>
-    <t>https://tjaanalyzer-ja.ckq.me/</t>
-  </si>
-  <si>
-    <t>TaikoImager</t>
-  </si>
-  <si>
-    <t>可以获得还原官方视觉效果的谱面片段或谱面图，支持各种演奏选项</t>
-  </si>
-  <si>
-    <t>AI定数预测</t>
-  </si>
-  <si>
-    <t>https://tjapre.haxif.com/</t>
-  </si>
-  <si>
-    <t>让AI对你创作的谱面进行难度的初步评估</t>
-  </si>
-  <si>
-    <t>kokoko.jpg</t>
-  </si>
-  <si>
-    <t>菌菌控制台</t>
-  </si>
-  <si>
-    <t>https://kinoko.zorua.cn/</t>
-  </si>
-  <si>
-    <t>菌菌控制台！可以管理自己的成绩以及使用菌菌的多项隐藏功能！</t>
-  </si>
-  <si>
-    <t>junjun.png</t>
-  </si>
-  <si>
-    <t>菌菌别名表格</t>
-  </si>
-  <si>
-    <t>https://www.kdocs.cn/l/cauSVZId2ohu</t>
-  </si>
-  <si>
-    <t>Sakura Bot</t>
-  </si>
-  <si>
-    <t>https://viewer.sakura-bot.cn/</t>
-  </si>
-  <si>
-    <t>猫鼓的小店</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.8ceeLYiw0FAY9K7</t>
-  </si>
-  <si>
-    <t>cat.png</t>
-  </si>
-  <si>
-    <t>Power的小店</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.8Yfnk26SrA8pUqZ</t>
-  </si>
-  <si>
-    <t>power.png</t>
-  </si>
-  <si>
-    <t>鱼鼓的小店</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.81neAPV?tk=6DKIgHaFqR5</t>
-  </si>
-  <si>
-    <t>sakataiko.png</t>
-  </si>
-  <si>
-    <t>神童同学</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.8cJNqUO?tk=jmmEgH1Qo0i</t>
-  </si>
-  <si>
-    <t>stg.png</t>
-  </si>
-  <si>
-    <t>伪都特产私棍</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.81OScrk19TUpuPM</t>
-  </si>
-  <si>
-    <t>otto.png</t>
-  </si>
-  <si>
-    <t>单手全连逆战</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.8cqwDXa?tk=hurZgHYHZl1</t>
-  </si>
-  <si>
-    <t>nizhan.png</t>
-  </si>
-  <si>
-    <t>狂澜怒涛</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.8cqx9ES?tk=zVYNgHYHAvf</t>
-  </si>
-  <si>
-    <t>7f7f.png</t>
-  </si>
-  <si>
-    <t>西瓜的音游小铺</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.8Ys9Atv?tk=ZPbKgHYti3K</t>
-  </si>
-  <si>
-    <t>watermelon.png</t>
-  </si>
-  <si>
-    <t>ZDR</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.8210xIi?tk=yD8tgHYztMN</t>
-  </si>
-  <si>
-    <t>zdr.png</t>
-  </si>
-  <si>
-    <t>活体搁浅</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.81pdJXR?tk=0WqugHYwWq5</t>
-  </si>
-  <si>
-    <t>wai.jpg</t>
-  </si>
-  <si>
-    <t>不灭的灯</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.81pYYTI?tk=qfzFgHYu00f</t>
-  </si>
-  <si>
-    <t>deng.png</t>
-  </si>
-  <si>
-    <t>小言罐头</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.82YviOa?tk=oo9hgHYtJGQ</t>
-  </si>
-  <si>
-    <t>yan.png</t>
-  </si>
-  <si>
-    <t>哈基缘</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.8217LAp?tk=rOm4gH16WJD</t>
-  </si>
-  <si>
-    <t>yuan.png</t>
-  </si>
-  <si>
-    <t>小章木工坊</t>
-  </si>
-  <si>
-    <t>https://mobile.yangkeduo.com/mall_page.html?ps=IpGOWhdEwr</t>
-  </si>
-  <si>
-    <t>pdd.png</t>
-  </si>
-  <si>
-    <t>铭盛科技</t>
-  </si>
-  <si>
-    <t>https://e.tb.cn/h.8XcgB01nntTZ3dL?tk=AyHygHkEYP4</t>
-  </si>
-  <si>
-    <t>mingsheng.png</t>
-  </si>
-  <si>
-    <t>太鼓之达人官方</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>太鼓之达人官方Bilibili账号</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>华立电竞官方Bilibili账号</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>太鼓Fandom</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>全国玩家群</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>全国范围的2000人玩家交流群</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>太鼓WIKI 日</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>太鼓WIKI 韩</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>PeepoDrumKit</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Database定数</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>华立官方淘汰的次品官机配件，可以尝试抽奖</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>20元以内性价比首选，建议选圆头枫木，自己购置手胶</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>为歌曲添加别名用于菌菌的歌曲查询</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://imager.donders.work</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://rating.haxif.com</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>AI Rating分析</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>让AI对你的成绩信息进行分析总结</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>stv.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://stevetaikocon.stevexmh.net/</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>控制器调试辅助</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.84CuZpo?tk=wIPJgCL06NC</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>StevenXMH</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>kokoko.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://wiki.ourtaiko.org/songs</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>OurtaikoWiki</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>国内玩家开发的成绩评分系统及谱面查询</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>可可子</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://kkz.haxif.com/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://taikonauts-docs.pages.dev</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.79bc2456WMXQuw&amp;userId=1814109102</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>napZ</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>za.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZA鼓以及各种太鼓配件</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -640,7 +698,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -818,6 +876,36 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC66"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF5050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1068,11 +1156,41 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" xfId="42" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" xfId="42" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" xfId="42" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" xfId="42" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1123,6 +1241,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFFF00"/>
+      <color rgb="FFFF5050"/>
+      <color rgb="FFFFCC66"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1451,7 +1576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2205B9E-1FE6-4EB7-B604-2CFC0207A242}">
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.5546875" customWidth="1"/>
@@ -1478,290 +1603,302 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2">
+      <c r="C2" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="A6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6">
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D7" t="s">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>121</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="A8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C8" t="s">
-        <v>122</v>
-      </c>
-      <c r="D8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8">
+      <c r="C8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>141</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="A10" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>126</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B14" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E14" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D14" t="s">
+      <c r="C15" s="5"/>
+      <c r="D15" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E14">
+      <c r="E15" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D15" t="s">
+      <c r="C16" s="5"/>
+      <c r="D16" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E15">
+      <c r="E16" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D16" t="s">
+      <c r="C17" s="5"/>
+      <c r="D17" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E16">
+      <c r="C18" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>125</v>
-      </c>
-      <c r="B18" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C18" t="s">
+      <c r="B19" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D18" t="s">
+      <c r="C19" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E18">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="D19" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19">
+      <c r="E19" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>49</v>
-      </c>
-      <c r="B20" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" t="s">
+        <v>54</v>
       </c>
       <c r="D20" t="s">
         <v>6</v>
@@ -1771,28 +1908,28 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>51</v>
-      </c>
-      <c r="B21" t="s">
-        <v>52</v>
+      <c r="A21" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>141</v>
       </c>
       <c r="D21" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21">
+        <v>139</v>
+      </c>
+      <c r="E21" s="10">
         <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D22" t="s">
         <v>6</v>
@@ -1803,10 +1940,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D23" t="s">
         <v>6</v>
@@ -1817,13 +1954,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D24" t="s">
         <v>6</v>
@@ -1834,13 +1971,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>136</v>
+        <v>52</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D25" t="s">
-        <v>134</v>
+        <v>6</v>
       </c>
       <c r="E25">
         <v>4</v>
@@ -1848,16 +1985,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C26" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="D26" t="s">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="E26">
         <v>4</v>
@@ -1865,16 +1999,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" t="s">
-        <v>61</v>
+        <v>106</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="E27">
         <v>4</v>
@@ -1882,305 +2016,375 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C28" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E29" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E30" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B31" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C31" s="6"/>
+      <c r="D31" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E31" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E32" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D28" t="s">
+      <c r="B33" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="E28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="E33" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B29" t="s">
+      <c r="E34" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="E35" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C29" t="s">
+      <c r="E36" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E37" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E38" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B39" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="D29" t="s">
-        <v>67</v>
-      </c>
-      <c r="E29">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>70</v>
-      </c>
-      <c r="B30" t="s">
-        <v>71</v>
-      </c>
-      <c r="D30" t="s">
-        <v>6</v>
-      </c>
-      <c r="E30">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>143</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="D31" t="s">
-        <v>139</v>
-      </c>
-      <c r="E31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="C39" s="8"/>
+      <c r="D39" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B32" t="s">
+      <c r="E39" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="D32" t="s">
+      <c r="B40" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="E32">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="E40" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B41" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E41" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="E33">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="E42" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B43" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E43" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="E34">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>138</v>
-      </c>
-      <c r="B35" s="1" t="s">
+      <c r="B44" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E44" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E45" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E46" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E47" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E48" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B49" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="D35" t="s">
-        <v>134</v>
-      </c>
-      <c r="E35">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>81</v>
-      </c>
-      <c r="B36" t="s">
-        <v>82</v>
-      </c>
-      <c r="D36" t="s">
-        <v>83</v>
-      </c>
-      <c r="E36">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>84</v>
-      </c>
-      <c r="B37" t="s">
-        <v>85</v>
-      </c>
-      <c r="D37" t="s">
-        <v>86</v>
-      </c>
-      <c r="E37">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>87</v>
-      </c>
-      <c r="B38" t="s">
-        <v>88</v>
-      </c>
-      <c r="D38" t="s">
-        <v>89</v>
-      </c>
-      <c r="E38">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="C49" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D49" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="B39" t="s">
-        <v>91</v>
-      </c>
-      <c r="D39" t="s">
-        <v>92</v>
-      </c>
-      <c r="E39">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>93</v>
-      </c>
-      <c r="B40" t="s">
-        <v>94</v>
-      </c>
-      <c r="D40" t="s">
-        <v>95</v>
-      </c>
-      <c r="E40">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>96</v>
-      </c>
-      <c r="B41" t="s">
-        <v>97</v>
-      </c>
-      <c r="D41" t="s">
-        <v>98</v>
-      </c>
-      <c r="E41">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>99</v>
-      </c>
-      <c r="B42" t="s">
-        <v>100</v>
-      </c>
-      <c r="D42" t="s">
-        <v>101</v>
-      </c>
-      <c r="E42">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>102</v>
-      </c>
-      <c r="B43" t="s">
-        <v>103</v>
-      </c>
-      <c r="D43" t="s">
-        <v>104</v>
-      </c>
-      <c r="E43">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>105</v>
-      </c>
-      <c r="B44" t="s">
-        <v>106</v>
-      </c>
-      <c r="D44" t="s">
-        <v>107</v>
-      </c>
-      <c r="E44">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>108</v>
-      </c>
-      <c r="B45" t="s">
-        <v>109</v>
-      </c>
-      <c r="D45" t="s">
-        <v>110</v>
-      </c>
-      <c r="E45">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>111</v>
-      </c>
-      <c r="B46" t="s">
-        <v>112</v>
-      </c>
-      <c r="C46" t="s">
-        <v>128</v>
-      </c>
-      <c r="D46" t="s">
-        <v>113</v>
-      </c>
-      <c r="E46">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>114</v>
-      </c>
-      <c r="B47" t="s">
-        <v>115</v>
-      </c>
-      <c r="C47" t="s">
-        <v>127</v>
-      </c>
-      <c r="D47" t="s">
-        <v>116</v>
-      </c>
-      <c r="E47">
+      <c r="E49" s="8">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B24" r:id="rId1" xr:uid="{0814D534-9BBD-4FF2-91BF-D9D2FA195367}"/>
-    <hyperlink ref="B26" r:id="rId2" xr:uid="{1C29CD7D-8195-4F43-BF25-3937379C553D}"/>
-    <hyperlink ref="B25" r:id="rId3" xr:uid="{C7DC1DD1-A540-4732-A529-6E4F4FC7E8F3}"/>
-    <hyperlink ref="B35" r:id="rId4" xr:uid="{CACBC6E3-169E-4706-B683-51554D0D68AD}"/>
+    <hyperlink ref="B20" r:id="rId1" xr:uid="{0814D534-9BBD-4FF2-91BF-D9D2FA195367}"/>
+    <hyperlink ref="B27" r:id="rId2" xr:uid="{1C29CD7D-8195-4F43-BF25-3937379C553D}"/>
+    <hyperlink ref="B26" r:id="rId3" xr:uid="{C7DC1DD1-A540-4732-A529-6E4F4FC7E8F3}"/>
+    <hyperlink ref="B37" r:id="rId4" xr:uid="{CACBC6E3-169E-4706-B683-51554D0D68AD}"/>
     <hyperlink ref="B10" r:id="rId5" xr:uid="{E4702D2D-6FCD-4B5B-9E81-602FCFEC045E}"/>
-    <hyperlink ref="B31" r:id="rId6" xr:uid="{A1F7C2BA-EE73-4EAF-99B5-5E02AFC9E006}"/>
+    <hyperlink ref="B32" r:id="rId6" xr:uid="{A1F7C2BA-EE73-4EAF-99B5-5E02AFC9E006}"/>
+    <hyperlink ref="B33" r:id="rId7" xr:uid="{AE381AE9-C7E3-48F7-BEC9-7DABD944D317}"/>
+    <hyperlink ref="B34" r:id="rId8" xr:uid="{FA0E93C8-8380-4554-B1AF-7A314C12F0F0}"/>
+    <hyperlink ref="B40" r:id="rId9" xr:uid="{95CEEF74-399F-4BB0-84CC-A80EC975FADE}"/>
+    <hyperlink ref="B46" r:id="rId10" xr:uid="{1243E3BB-84D1-4ACA-9021-EE8FCA8830B3}"/>
+    <hyperlink ref="B36" r:id="rId11" xr:uid="{B8B71B7B-0A03-4E4B-847B-71311DFEDCA0}"/>
+    <hyperlink ref="B43" r:id="rId12" xr:uid="{F77A6A42-7643-4489-98B0-ABE8B87CF767}"/>
+    <hyperlink ref="B42" r:id="rId13" xr:uid="{6B2D5271-7CC5-4F08-AB0C-B89338B4A63C}"/>
+    <hyperlink ref="B41" r:id="rId14" xr:uid="{6D333F99-D332-4EAB-BF65-094492050942}"/>
+    <hyperlink ref="B39" r:id="rId15" xr:uid="{C33A6450-F262-44B1-AFB0-3337948BF9A0}"/>
+    <hyperlink ref="B38" r:id="rId16" xr:uid="{B7F01162-C6EA-409F-B151-19867DBC753A}"/>
+    <hyperlink ref="B44" r:id="rId17" xr:uid="{B243319D-2D2D-4A67-B44E-198D616C4C29}"/>
+    <hyperlink ref="B45" r:id="rId18" xr:uid="{52F90D2B-5B0E-456F-9F77-3826408A3A90}"/>
+    <hyperlink ref="B47" r:id="rId19" xr:uid="{4A20EF09-9308-4377-92A2-06F8794335E9}"/>
+    <hyperlink ref="B49" r:id="rId20" xr:uid="{CB8B7E6A-16D0-4487-95BC-BBCDB1DDB762}"/>
+    <hyperlink ref="B21" r:id="rId21" xr:uid="{2AA1A8B2-65B5-4DFD-AE88-E03CD884F638}"/>
+    <hyperlink ref="B25" r:id="rId22" xr:uid="{7CFFC6E2-2149-496D-87C9-33DB97F87074}"/>
+    <hyperlink ref="B24" r:id="rId23" xr:uid="{4389E72A-7A4A-4C46-9BB9-695300B8D532}"/>
+    <hyperlink ref="B28" r:id="rId24" xr:uid="{3C38A248-15F8-4BCA-BE67-A17C6DD580AA}"/>
+    <hyperlink ref="B14" r:id="rId25" xr:uid="{149FD85D-6BAC-4E79-965A-4E1DB371554D}"/>
+    <hyperlink ref="B35" r:id="rId26" xr:uid="{85A892E7-4CC8-416A-B056-F80EE05A2D41}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\TaikoNavigation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B511739D-B248-4126-BD16-58E6164312D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF5DAAD-196A-4D51-B0CC-FDF46F0D337A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{21938866-CF94-43A1-8F72-DCC95449F496}"/>
   </bookViews>
@@ -483,10 +483,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>TjaVideoPlayer</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>0.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -540,6 +536,10 @@
   </si>
   <si>
     <t>ZA鼓以及各种太鼓配件</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TJA2Video</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1156,7 +1156,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1185,9 +1185,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="37" borderId="0" xfId="42" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="35" borderId="0" xfId="42" applyFill="1">
@@ -1798,14 +1795,14 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>148</v>
+        <v>141</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>147</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E14" s="5">
         <v>3</v>
@@ -1908,19 +1905,19 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
+      <c r="A21" t="s">
+        <v>152</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C21" t="s">
+        <v>140</v>
+      </c>
+      <c r="D21" t="s">
         <v>138</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="D21" t="s">
-        <v>139</v>
-      </c>
-      <c r="E21" s="10">
+      <c r="E21">
         <v>4</v>
       </c>
     </row>
@@ -1957,7 +1954,7 @@
         <v>50</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C24" t="s">
         <v>51</v>
@@ -1974,7 +1971,7 @@
         <v>52</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D25" t="s">
         <v>6</v>
@@ -1988,7 +1985,7 @@
         <v>109</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D26" t="s">
         <v>108</v>
@@ -2019,7 +2016,7 @@
         <v>55</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C28" t="s">
         <v>56</v>
@@ -2127,16 +2124,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="D35" s="8" t="s">
         <v>150</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>151</v>
       </c>
       <c r="E35" s="8">
         <v>6</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\TaikoNavigation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF5DAAD-196A-4D51-B0CC-FDF46F0D337A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0027C5BF-8663-4BA1-A517-9215FB03A4CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{21938866-CF94-43A1-8F72-DCC95449F496}"/>
   </bookViews>
@@ -483,10 +483,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>0.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>https://video.donders.work</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -540,6 +536,10 @@
   </si>
   <si>
     <t>TJA2Video</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TJA2Video.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1795,14 +1795,14 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E14" s="5">
         <v>3</v>
@@ -1906,16 +1906,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>151</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C21" t="s">
+        <v>139</v>
+      </c>
+      <c r="D21" t="s">
         <v>152</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C21" t="s">
-        <v>140</v>
-      </c>
-      <c r="D21" t="s">
-        <v>138</v>
       </c>
       <c r="E21">
         <v>4</v>
@@ -1954,7 +1954,7 @@
         <v>50</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C24" t="s">
         <v>51</v>
@@ -1971,7 +1971,7 @@
         <v>52</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D25" t="s">
         <v>6</v>
@@ -1985,7 +1985,7 @@
         <v>109</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D26" t="s">
         <v>108</v>
@@ -2016,7 +2016,7 @@
         <v>55</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C28" t="s">
         <v>56</v>
@@ -2124,16 +2124,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D35" s="8" t="s">
         <v>149</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>150</v>
       </c>
       <c r="E35" s="8">
         <v>6</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,26 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\TaikoNavigation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0027C5BF-8663-4BA1-A517-9215FB03A4CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A86B6F-46B5-4433-87DB-B6216A26DF41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{21938866-CF94-43A1-8F72-DCC95449F496}"/>
+    <workbookView xWindow="7920" yWindow="1728" windowWidth="12756" windowHeight="13560" xr2:uid="{21938866-CF94-43A1-8F72-DCC95449F496}"/>
   </bookViews>
   <sheets>
-    <sheet name="deepseek_csv_20260722_b23856" sheetId="1" r:id="rId1"/>
+    <sheet name="主页" sheetId="1" r:id="rId1"/>
+    <sheet name="自制谱专区" sheetId="3" r:id="rId2"/>
+    <sheet name="家用鼓选购" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="157">
   <si>
     <t>name</t>
   </si>
@@ -540,6 +542,22 @@
   </si>
   <si>
     <t>TJA2Video.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://fanmade.ourtaiko.org/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OurTaikoFanmade</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>中国自制谱社区</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>FanMade.ico</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1573,7 +1591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2205B9E-1FE6-4EB7-B604-2CFC0207A242}">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.5546875" customWidth="1"/>
@@ -1825,14 +1843,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="5"/>
+        <v>154</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>155</v>
+      </c>
       <c r="D16" s="5" t="s">
-        <v>36</v>
+        <v>156</v>
       </c>
       <c r="E16" s="5">
         <v>3</v>
@@ -1840,14 +1860,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="5"/>
+        <v>39</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="D17" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E17" s="5">
         <v>3</v>
@@ -1855,16 +1877,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E18" s="5">
         <v>3</v>
@@ -1872,50 +1894,46 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>44</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="C19" s="5"/>
       <c r="D19" s="5" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E19" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20">
-        <v>4</v>
+      <c r="A20" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>151</v>
+        <v>53</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
-        <v>139</v>
+        <v>54</v>
       </c>
       <c r="D21" t="s">
-        <v>152</v>
+        <v>6</v>
       </c>
       <c r="E21">
         <v>4</v>
@@ -1923,13 +1941,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" t="s">
-        <v>47</v>
+        <v>151</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C22" t="s">
+        <v>139</v>
       </c>
       <c r="D22" t="s">
-        <v>6</v>
+        <v>152</v>
       </c>
       <c r="E22">
         <v>4</v>
@@ -1937,10 +1958,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D23" t="s">
         <v>6</v>
@@ -1951,13 +1972,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>50</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C24" t="s">
-        <v>51</v>
+        <v>48</v>
+      </c>
+      <c r="B24" t="s">
+        <v>49</v>
       </c>
       <c r="D24" t="s">
         <v>6</v>
@@ -1968,10 +1986,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
+      </c>
+      <c r="C25" t="s">
+        <v>51</v>
       </c>
       <c r="D25" t="s">
         <v>6</v>
@@ -1982,13 +2003,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>109</v>
+        <v>52</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D26" t="s">
-        <v>108</v>
+        <v>6</v>
       </c>
       <c r="E26">
         <v>4</v>
@@ -1996,16 +2017,13 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C27" t="s">
-        <v>107</v>
+        <v>143</v>
       </c>
       <c r="D27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E27">
         <v>4</v>
@@ -2013,47 +2031,47 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="C28" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="D28" t="s">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="E28">
         <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E29" s="6">
-        <v>5</v>
+      <c r="A29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C29" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" t="s">
+        <v>57</v>
+      </c>
+      <c r="E29">
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>103</v>
+        <v>60</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>61</v>
@@ -2064,14 +2082,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" s="6"/>
+        <v>63</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>103</v>
+      </c>
       <c r="D31" s="6" t="s">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="E31" s="6">
         <v>5</v>
@@ -2079,44 +2099,44 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>116</v>
+        <v>64</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="6" t="s">
-        <v>111</v>
+        <v>6</v>
       </c>
       <c r="E32" s="6">
         <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="E33" s="8">
-        <v>6</v>
+      <c r="A33" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E33" s="6">
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E34" s="8">
         <v>6</v>
@@ -2124,16 +2144,14 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>150</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="C35" s="8"/>
       <c r="D35" s="8" t="s">
-        <v>149</v>
+        <v>68</v>
       </c>
       <c r="E35" s="8">
         <v>6</v>
@@ -2141,14 +2159,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C36" s="8"/>
+        <v>147</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>150</v>
+      </c>
       <c r="D36" s="8" t="s">
-        <v>69</v>
+        <v>149</v>
       </c>
       <c r="E36" s="8">
         <v>6</v>
@@ -2156,14 +2176,14 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="8" t="s">
-        <v>108</v>
+        <v>69</v>
       </c>
       <c r="E37" s="8">
         <v>6</v>
@@ -2171,14 +2191,14 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="E38" s="8">
         <v>6</v>
@@ -2186,14 +2206,14 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E39" s="8">
         <v>6</v>
@@ -2201,14 +2221,14 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E40" s="8">
         <v>6</v>
@@ -2216,14 +2236,14 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E41" s="8">
         <v>6</v>
@@ -2231,14 +2251,14 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E42" s="8">
         <v>6</v>
@@ -2246,14 +2266,14 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E43" s="8">
         <v>6</v>
@@ -2261,14 +2281,14 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E44" s="8">
         <v>6</v>
@@ -2276,14 +2296,14 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E45" s="8">
         <v>6</v>
@@ -2291,14 +2311,14 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
-        <v>83</v>
+        <v>132</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E46" s="8">
         <v>6</v>
@@ -2306,14 +2326,14 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E47" s="8">
         <v>6</v>
@@ -2321,16 +2341,14 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>102</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="C48" s="8"/>
       <c r="D48" s="8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E48" s="8">
         <v>6</v>
@@ -2338,50 +2356,408 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E49" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B50" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="C49" s="8" t="s">
+      <c r="C50" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D49" s="8" t="s">
+      <c r="D50" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="E49" s="8">
+      <c r="E50" s="8">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B20" r:id="rId1" xr:uid="{0814D534-9BBD-4FF2-91BF-D9D2FA195367}"/>
-    <hyperlink ref="B27" r:id="rId2" xr:uid="{1C29CD7D-8195-4F43-BF25-3937379C553D}"/>
-    <hyperlink ref="B26" r:id="rId3" xr:uid="{C7DC1DD1-A540-4732-A529-6E4F4FC7E8F3}"/>
-    <hyperlink ref="B37" r:id="rId4" xr:uid="{CACBC6E3-169E-4706-B683-51554D0D68AD}"/>
+    <hyperlink ref="B21" r:id="rId1" xr:uid="{0814D534-9BBD-4FF2-91BF-D9D2FA195367}"/>
+    <hyperlink ref="B28" r:id="rId2" xr:uid="{1C29CD7D-8195-4F43-BF25-3937379C553D}"/>
+    <hyperlink ref="B27" r:id="rId3" xr:uid="{C7DC1DD1-A540-4732-A529-6E4F4FC7E8F3}"/>
+    <hyperlink ref="B38" r:id="rId4" xr:uid="{CACBC6E3-169E-4706-B683-51554D0D68AD}"/>
     <hyperlink ref="B10" r:id="rId5" xr:uid="{E4702D2D-6FCD-4B5B-9E81-602FCFEC045E}"/>
-    <hyperlink ref="B32" r:id="rId6" xr:uid="{A1F7C2BA-EE73-4EAF-99B5-5E02AFC9E006}"/>
-    <hyperlink ref="B33" r:id="rId7" xr:uid="{AE381AE9-C7E3-48F7-BEC9-7DABD944D317}"/>
-    <hyperlink ref="B34" r:id="rId8" xr:uid="{FA0E93C8-8380-4554-B1AF-7A314C12F0F0}"/>
-    <hyperlink ref="B40" r:id="rId9" xr:uid="{95CEEF74-399F-4BB0-84CC-A80EC975FADE}"/>
-    <hyperlink ref="B46" r:id="rId10" xr:uid="{1243E3BB-84D1-4ACA-9021-EE8FCA8830B3}"/>
-    <hyperlink ref="B36" r:id="rId11" xr:uid="{B8B71B7B-0A03-4E4B-847B-71311DFEDCA0}"/>
-    <hyperlink ref="B43" r:id="rId12" xr:uid="{F77A6A42-7643-4489-98B0-ABE8B87CF767}"/>
-    <hyperlink ref="B42" r:id="rId13" xr:uid="{6B2D5271-7CC5-4F08-AB0C-B89338B4A63C}"/>
-    <hyperlink ref="B41" r:id="rId14" xr:uid="{6D333F99-D332-4EAB-BF65-094492050942}"/>
-    <hyperlink ref="B39" r:id="rId15" xr:uid="{C33A6450-F262-44B1-AFB0-3337948BF9A0}"/>
-    <hyperlink ref="B38" r:id="rId16" xr:uid="{B7F01162-C6EA-409F-B151-19867DBC753A}"/>
-    <hyperlink ref="B44" r:id="rId17" xr:uid="{B243319D-2D2D-4A67-B44E-198D616C4C29}"/>
-    <hyperlink ref="B45" r:id="rId18" xr:uid="{52F90D2B-5B0E-456F-9F77-3826408A3A90}"/>
-    <hyperlink ref="B47" r:id="rId19" xr:uid="{4A20EF09-9308-4377-92A2-06F8794335E9}"/>
-    <hyperlink ref="B49" r:id="rId20" xr:uid="{CB8B7E6A-16D0-4487-95BC-BBCDB1DDB762}"/>
-    <hyperlink ref="B21" r:id="rId21" xr:uid="{2AA1A8B2-65B5-4DFD-AE88-E03CD884F638}"/>
-    <hyperlink ref="B25" r:id="rId22" xr:uid="{7CFFC6E2-2149-496D-87C9-33DB97F87074}"/>
-    <hyperlink ref="B24" r:id="rId23" xr:uid="{4389E72A-7A4A-4C46-9BB9-695300B8D532}"/>
-    <hyperlink ref="B28" r:id="rId24" xr:uid="{3C38A248-15F8-4BCA-BE67-A17C6DD580AA}"/>
+    <hyperlink ref="B33" r:id="rId6" xr:uid="{A1F7C2BA-EE73-4EAF-99B5-5E02AFC9E006}"/>
+    <hyperlink ref="B34" r:id="rId7" xr:uid="{AE381AE9-C7E3-48F7-BEC9-7DABD944D317}"/>
+    <hyperlink ref="B35" r:id="rId8" xr:uid="{FA0E93C8-8380-4554-B1AF-7A314C12F0F0}"/>
+    <hyperlink ref="B41" r:id="rId9" xr:uid="{95CEEF74-399F-4BB0-84CC-A80EC975FADE}"/>
+    <hyperlink ref="B47" r:id="rId10" xr:uid="{1243E3BB-84D1-4ACA-9021-EE8FCA8830B3}"/>
+    <hyperlink ref="B37" r:id="rId11" xr:uid="{B8B71B7B-0A03-4E4B-847B-71311DFEDCA0}"/>
+    <hyperlink ref="B44" r:id="rId12" xr:uid="{F77A6A42-7643-4489-98B0-ABE8B87CF767}"/>
+    <hyperlink ref="B43" r:id="rId13" xr:uid="{6B2D5271-7CC5-4F08-AB0C-B89338B4A63C}"/>
+    <hyperlink ref="B42" r:id="rId14" xr:uid="{6D333F99-D332-4EAB-BF65-094492050942}"/>
+    <hyperlink ref="B40" r:id="rId15" xr:uid="{C33A6450-F262-44B1-AFB0-3337948BF9A0}"/>
+    <hyperlink ref="B39" r:id="rId16" xr:uid="{B7F01162-C6EA-409F-B151-19867DBC753A}"/>
+    <hyperlink ref="B45" r:id="rId17" xr:uid="{B243319D-2D2D-4A67-B44E-198D616C4C29}"/>
+    <hyperlink ref="B46" r:id="rId18" xr:uid="{52F90D2B-5B0E-456F-9F77-3826408A3A90}"/>
+    <hyperlink ref="B48" r:id="rId19" xr:uid="{4A20EF09-9308-4377-92A2-06F8794335E9}"/>
+    <hyperlink ref="B50" r:id="rId20" xr:uid="{CB8B7E6A-16D0-4487-95BC-BBCDB1DDB762}"/>
+    <hyperlink ref="B22" r:id="rId21" xr:uid="{2AA1A8B2-65B5-4DFD-AE88-E03CD884F638}"/>
+    <hyperlink ref="B26" r:id="rId22" xr:uid="{7CFFC6E2-2149-496D-87C9-33DB97F87074}"/>
+    <hyperlink ref="B25" r:id="rId23" xr:uid="{4389E72A-7A4A-4C46-9BB9-695300B8D532}"/>
+    <hyperlink ref="B29" r:id="rId24" xr:uid="{3C38A248-15F8-4BCA-BE67-A17C6DD580AA}"/>
     <hyperlink ref="B14" r:id="rId25" xr:uid="{149FD85D-6BAC-4E79-965A-4E1DB371554D}"/>
-    <hyperlink ref="B35" r:id="rId26" xr:uid="{85A892E7-4CC8-416A-B056-F80EE05A2D41}"/>
+    <hyperlink ref="B36" r:id="rId26" xr:uid="{85A892E7-4CC8-416A-B056-F80EE05A2D41}"/>
+    <hyperlink ref="B16" r:id="rId27" xr:uid="{B75FED28-B2A5-4AA7-BB1A-A29CA62218B9}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E47D55AA-24E1-48BD-B118-4FFFED8D4060}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.5546875" customWidth="1"/>
+    <col min="2" max="2" width="51.33203125" customWidth="1"/>
+    <col min="3" max="3" width="64.77734375" customWidth="1"/>
+    <col min="4" max="4" width="20.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E5" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D8" t="s">
+        <v>152</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{74592461-ECB0-4B8D-ADD2-990A8287FC80}"/>
+    <hyperlink ref="B8" r:id="rId2" xr:uid="{AE56E8A3-6574-4E6B-B527-C389062FFD5F}"/>
+    <hyperlink ref="B10" r:id="rId3" xr:uid="{95DC152E-AFF6-4E14-9FC8-D4457BF39508}"/>
+    <hyperlink ref="B9" r:id="rId4" xr:uid="{BEC94B9C-7E51-4B59-A597-F4F3FFE535B4}"/>
+    <hyperlink ref="B11" r:id="rId5" xr:uid="{FE1E462D-1567-4115-901B-5355F3B6C74D}"/>
+    <hyperlink ref="B3" r:id="rId6" xr:uid="{1679D661-FBFE-497E-9C50-301AAF57BCA4}"/>
+    <hyperlink ref="B5" r:id="rId7" xr:uid="{A773D842-D985-4CC7-A96C-ECE986F688CC}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85318208-7F6B-460C-BEFD-B6FCAA294D89}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.5546875" customWidth="1"/>
+    <col min="2" max="2" width="51.33203125" customWidth="1"/>
+    <col min="3" max="3" width="64.77734375" customWidth="1"/>
+    <col min="4" max="4" width="20.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="E4" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E6" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="8">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{B445E6B6-B847-495D-B6A5-26A68D515FFE}"/>
+    <hyperlink ref="B2" r:id="rId2" xr:uid="{BBEDAB73-3045-4443-84BB-B219DDB1E215}"/>
+    <hyperlink ref="B3" r:id="rId3" xr:uid="{A1BB8353-AEB9-4C7B-92F7-D0E822EDD0D8}"/>
+    <hyperlink ref="B5" r:id="rId4" xr:uid="{80BC0C96-4DBE-434F-9EB7-7FB33A501B50}"/>
+    <hyperlink ref="B7" r:id="rId5" xr:uid="{DE20E162-65FE-43C8-A3D5-3732E04DE2C2}"/>
+    <hyperlink ref="B4" r:id="rId6" xr:uid="{EDA0D7A9-D5C9-4E56-88F5-680DD9ED7DA6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\TaikoNavigation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A86B6F-46B5-4433-87DB-B6216A26DF41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9701227A-C890-4E01-ACD1-493A70A4BE54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7920" yWindow="1728" windowWidth="12756" windowHeight="13560" xr2:uid="{21938866-CF94-43A1-8F72-DCC95449F496}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{21938866-CF94-43A1-8F72-DCC95449F496}"/>
   </bookViews>
   <sheets>
     <sheet name="主页" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="163">
   <si>
     <t>name</t>
   </si>
@@ -558,6 +558,30 @@
   </si>
   <si>
     <t>FanMade.ico</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>制谱器</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>linetitle</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>自制谱社区</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>谱面预览生成</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>模拟器</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2425,7 +2449,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E47D55AA-24E1-48BD-B118-4FFFED8D4060}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.5546875" customWidth="1"/>
@@ -2452,50 +2476,36 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="5">
-        <v>3</v>
+      <c r="A2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E2" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="C3" s="5"/>
+        <v>99</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="D3" s="5" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E3" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="5">
-        <v>3</v>
+      <c r="A4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E4" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2516,20 +2526,11 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="5">
-        <v>3</v>
+      <c r="A6" t="s">
+        <v>160</v>
+      </c>
+      <c r="E6" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2599,18 +2600,81 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>161</v>
+      </c>
+      <c r="E11" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E12" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>162</v>
+      </c>
+      <c r="E15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C16" t="s">
         <v>56</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D16" t="s">
         <v>57</v>
       </c>
-      <c r="E11">
+      <c r="E16">
         <v>4</v>
       </c>
     </row>
@@ -2621,8 +2685,8 @@
     <hyperlink ref="B8" r:id="rId2" xr:uid="{AE56E8A3-6574-4E6B-B527-C389062FFD5F}"/>
     <hyperlink ref="B10" r:id="rId3" xr:uid="{95DC152E-AFF6-4E14-9FC8-D4457BF39508}"/>
     <hyperlink ref="B9" r:id="rId4" xr:uid="{BEC94B9C-7E51-4B59-A597-F4F3FFE535B4}"/>
-    <hyperlink ref="B11" r:id="rId5" xr:uid="{FE1E462D-1567-4115-901B-5355F3B6C74D}"/>
-    <hyperlink ref="B3" r:id="rId6" xr:uid="{1679D661-FBFE-497E-9C50-301AAF57BCA4}"/>
+    <hyperlink ref="B16" r:id="rId5" xr:uid="{FE1E462D-1567-4115-901B-5355F3B6C74D}"/>
+    <hyperlink ref="B12" r:id="rId6" xr:uid="{1679D661-FBFE-497E-9C50-301AAF57BCA4}"/>
     <hyperlink ref="B5" r:id="rId7" xr:uid="{A773D842-D985-4CC7-A96C-ECE986F688CC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\TaikoNavigation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9701227A-C890-4E01-ACD1-493A70A4BE54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD0CC25-7DC5-4067-A59E-0066665B5E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{21938866-CF94-43A1-8F72-DCC95449F496}"/>
+    <workbookView xWindow="3684" yWindow="4812" windowWidth="25476" windowHeight="13560" activeTab="1" xr2:uid="{21938866-CF94-43A1-8F72-DCC95449F496}"/>
   </bookViews>
   <sheets>
     <sheet name="主页" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="170">
   <si>
     <t>name</t>
   </si>
@@ -171,9 +171,6 @@
     <t>Donder Asistant</t>
   </si>
   <si>
-    <t>https://dafrok.github.io/donder-assistant/analysis</t>
-  </si>
-  <si>
     <t>Tja-Tools</t>
   </si>
   <si>
@@ -345,243 +342,275 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>https://imager.donders.work</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://rating.haxif.com</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI Rating分析</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>让AI对你的成绩信息进行分析总结</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>stv.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>控制器调试辅助</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>StevenXMH</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>kokoko.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://wiki.ourtaiko.org/songs</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OurtaikoWiki</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>国内玩家开发的成绩评分系统及谱面查询</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>可可子</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://kkz.haxif.com/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://shop525820965.taobao.com/category.htm?spm=pc_detail.30350276.shop_block.dshopinfo.56be7dd6dsI5yg&amp;topIds=719510077825</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Power的小店</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://shop104239116.taobao.com/category.htm?spm=pc_detail.30350276.shop_block.dshopinfo.6d1c6252j87z2N&amp;topIds=1050934996989</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>鱼鼓的小店</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.bought.0.0.5228252dPRFudb&amp;userId=3698605461</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.bought.0.0.5228252dPRFudb&amp;userId=1107549877</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>神童同学</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.27bd42b3JlfOmI&amp;userId=2709663921</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.6ad31a5as9AFCH&amp;userId=2213174146625</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>西瓜的音游小铺</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.12cf163dmL6Yrg&amp;userId=2135576311</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.46e4b2f2l91x1H&amp;userId=674644841</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://shop109402001.taobao.com/category.htm?spm=pc_detail.30350276.shop_block.dshopinfo.32217dd6Wwfp8W&amp;topIds=567063533860</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.52ca49fauX932Z&amp;userId=3704968269</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.19c73350BIZScL&amp;userId=3887875950</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>不灭的灯</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>哈基缘</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.150a505eFDpfwo&amp;userId=45429781</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.7dc67a0caZ3ysg&amp;userId=2200623233408</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.5b1052c7F1Fyox&amp;userId=2215320654516</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://e.tb.cn/h.8XcgB01nntTZ3dL?tk=AyHygHkEYP4</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://video.donders.work</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>将tja文件渲染为视频，便于分享</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TaikoNauts</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tjaanalyzer-ja.ckq.me</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://whmhammer.github.io/tja-tools</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://stevetaikocon.stevexmh.net</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tjapre.haxif.com</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TaikoNauts.ico</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://taikonauts-docs.pages.dev</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.79bc2456WMXQuw&amp;userId=1814109102</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>napZ</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>za.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZA鼓以及各种太鼓配件</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TJA2Video</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TJA2Video.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://fanmade.ourtaiko.org/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OurTaikoFanmade</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>中国自制谱社区</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>制谱器</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>linetitle</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>自制谱社区</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>谱面预览生成</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>模拟器</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>crt.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>fandom.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>oLaf.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>sakura.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OurTaiko.ico</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://dafrok.github.io/donder-assistant/constants</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>主营猫鼓、猫棍（榉木）</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>主营大力鼓、夯棍</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OurTaiko自制谱社区，可以在这里分享和体验太鼓自制谱</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>为歌曲添加别名用于菌菌的歌曲查询</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://imager.donders.work</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://rating.haxif.com</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>AI Rating分析</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>让AI对你的成绩信息进行分析总结</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>stv.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>控制器调试辅助</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>StevenXMH</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>kokoko.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://wiki.ourtaiko.org/songs</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>OurtaikoWiki</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>国内玩家开发的成绩评分系统及谱面查询</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>可可子</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://kkz.haxif.com/</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://shop525820965.taobao.com/category.htm?spm=pc_detail.30350276.shop_block.dshopinfo.56be7dd6dsI5yg&amp;topIds=719510077825</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Power的小店</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://shop104239116.taobao.com/category.htm?spm=pc_detail.30350276.shop_block.dshopinfo.6d1c6252j87z2N&amp;topIds=1050934996989</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>鱼鼓的小店</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.goofish.com/personal?spm=a21ybx.bought.0.0.5228252dPRFudb&amp;userId=3698605461</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.goofish.com/personal?spm=a21ybx.bought.0.0.5228252dPRFudb&amp;userId=1107549877</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>神童同学</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.27bd42b3JlfOmI&amp;userId=2709663921</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.6ad31a5as9AFCH&amp;userId=2213174146625</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>西瓜的音游小铺</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.12cf163dmL6Yrg&amp;userId=2135576311</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.46e4b2f2l91x1H&amp;userId=674644841</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://shop109402001.taobao.com/category.htm?spm=pc_detail.30350276.shop_block.dshopinfo.32217dd6Wwfp8W&amp;topIds=567063533860</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.52ca49fauX932Z&amp;userId=3704968269</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.19c73350BIZScL&amp;userId=3887875950</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>不灭的灯</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>哈基缘</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.150a505eFDpfwo&amp;userId=45429781</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.7dc67a0caZ3ysg&amp;userId=2200623233408</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.5b1052c7F1Fyox&amp;userId=2215320654516</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://e.tb.cn/h.8XcgB01nntTZ3dL?tk=AyHygHkEYP4</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://video.donders.work</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>将tja文件渲染为视频，便于分享</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>TaikoNauts</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tjaanalyzer-ja.ckq.me</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://whmhammer.github.io/tja-tools</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://stevetaikocon.stevexmh.net</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tjapre.haxif.com</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>TaikoNauts.ico</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://taikonauts-docs.pages.dev</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.79bc2456WMXQuw&amp;userId=1814109102</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>napZ</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>za.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ZA鼓以及各种太鼓配件</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>TJA2Video</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>TJA2Video.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://fanmade.ourtaiko.org/</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>OurTaikoFanmade</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>中国自制谱社区</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>FanMade.ico</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>制谱器</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>linetitle</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>自制谱社区</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>谱面预览生成</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>模拟器</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>其他</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1643,13 +1672,13 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>6</v>
@@ -1666,7 +1695,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>9</v>
@@ -1677,7 +1706,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>10</v>
@@ -1694,7 +1723,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>10</v>
@@ -1711,14 +1740,14 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>6</v>
+        <v>161</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
@@ -1741,16 +1770,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>6</v>
+        <v>160</v>
       </c>
       <c r="E8" s="2">
         <v>1</v>
@@ -1775,16 +1804,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="D10" s="3" t="s">
-        <v>6</v>
+        <v>164</v>
       </c>
       <c r="E10" s="3">
         <v>2</v>
@@ -1792,7 +1821,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>24</v>
@@ -1837,14 +1866,14 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E14" s="5">
         <v>3</v>
@@ -1867,16 +1896,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="E16" s="5">
         <v>3</v>
@@ -1884,7 +1913,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>39</v>
@@ -1948,13 +1977,13 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C21" t="s">
         <v>53</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C21" t="s">
-        <v>54</v>
       </c>
       <c r="D21" t="s">
         <v>6</v>
@@ -1965,16 +1994,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C22" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D22" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E22">
         <v>4</v>
@@ -1982,10 +2011,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C23" t="s">
+        <v>50</v>
       </c>
       <c r="D23" t="s">
         <v>6</v>
@@ -1996,10 +2028,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="D24" t="s">
         <v>6</v>
@@ -2010,13 +2042,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C25" t="s">
-        <v>51</v>
+        <v>165</v>
       </c>
       <c r="D25" t="s">
         <v>6</v>
@@ -2027,13 +2056,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>141</v>
+        <v>46</v>
+      </c>
+      <c r="B26" t="s">
+        <v>47</v>
       </c>
       <c r="D26" t="s">
-        <v>6</v>
+        <v>162</v>
       </c>
       <c r="E26">
         <v>4</v>
@@ -2041,13 +2070,13 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D27" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E27">
         <v>4</v>
@@ -2055,16 +2084,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C28" t="s">
         <v>105</v>
       </c>
-      <c r="C28" t="s">
-        <v>107</v>
-      </c>
       <c r="D28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E28">
         <v>4</v>
@@ -2072,16 +2101,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C29" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>56</v>
-      </c>
-      <c r="D29" t="s">
-        <v>57</v>
       </c>
       <c r="E29">
         <v>4</v>
@@ -2089,16 +2118,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="C30" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="D30" s="6" t="s">
         <v>60</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>61</v>
       </c>
       <c r="E30" s="6">
         <v>5</v>
@@ -2106,16 +2135,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>63</v>
-      </c>
       <c r="C31" s="6" t="s">
-        <v>103</v>
+        <v>169</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E31" s="6">
         <v>5</v>
@@ -2123,14 +2152,14 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>65</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="6" t="s">
-        <v>6</v>
+        <v>163</v>
       </c>
       <c r="E32" s="6">
         <v>5</v>
@@ -2138,14 +2167,14 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E33" s="6">
         <v>5</v>
@@ -2153,14 +2182,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="D34" s="8" t="s">
         <v>66</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8" t="s">
-        <v>67</v>
       </c>
       <c r="E34" s="8">
         <v>6</v>
@@ -2168,14 +2199,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="C35" s="8"/>
+        <v>117</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="D35" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E35" s="8">
         <v>6</v>
@@ -2183,16 +2216,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="D36" s="8" t="s">
         <v>147</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>149</v>
       </c>
       <c r="E36" s="8">
         <v>6</v>
@@ -2200,14 +2233,14 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E37" s="8">
         <v>6</v>
@@ -2215,14 +2248,14 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E38" s="8">
         <v>6</v>
@@ -2230,14 +2263,14 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E39" s="8">
         <v>6</v>
@@ -2245,14 +2278,14 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E40" s="8">
         <v>6</v>
@@ -2260,14 +2293,14 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E41" s="8">
         <v>6</v>
@@ -2275,14 +2308,14 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E42" s="8">
         <v>6</v>
@@ -2290,14 +2323,14 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E43" s="8">
         <v>6</v>
@@ -2305,14 +2338,14 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E44" s="8">
         <v>6</v>
@@ -2320,14 +2353,14 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E45" s="8">
         <v>6</v>
@@ -2335,14 +2368,14 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B46" s="9" t="s">
         <v>132</v>
-      </c>
-      <c r="B46" s="9" t="s">
-        <v>134</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E46" s="8">
         <v>6</v>
@@ -2350,14 +2383,14 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E47" s="8">
         <v>6</v>
@@ -2365,14 +2398,14 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B48" s="9" t="s">
         <v>133</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>135</v>
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E48" s="8">
         <v>6</v>
@@ -2380,16 +2413,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B49" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="C49" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D49" s="8" t="s">
         <v>87</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>88</v>
       </c>
       <c r="E49" s="8">
         <v>6</v>
@@ -2397,16 +2430,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D50" s="8" t="s">
         <v>89</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>90</v>
       </c>
       <c r="E50" s="8">
         <v>6</v>
@@ -2436,12 +2469,13 @@
     <hyperlink ref="B48" r:id="rId19" xr:uid="{4A20EF09-9308-4377-92A2-06F8794335E9}"/>
     <hyperlink ref="B50" r:id="rId20" xr:uid="{CB8B7E6A-16D0-4487-95BC-BBCDB1DDB762}"/>
     <hyperlink ref="B22" r:id="rId21" xr:uid="{2AA1A8B2-65B5-4DFD-AE88-E03CD884F638}"/>
-    <hyperlink ref="B26" r:id="rId22" xr:uid="{7CFFC6E2-2149-496D-87C9-33DB97F87074}"/>
-    <hyperlink ref="B25" r:id="rId23" xr:uid="{4389E72A-7A4A-4C46-9BB9-695300B8D532}"/>
+    <hyperlink ref="B24" r:id="rId22" xr:uid="{7CFFC6E2-2149-496D-87C9-33DB97F87074}"/>
+    <hyperlink ref="B23" r:id="rId23" xr:uid="{4389E72A-7A4A-4C46-9BB9-695300B8D532}"/>
     <hyperlink ref="B29" r:id="rId24" xr:uid="{3C38A248-15F8-4BCA-BE67-A17C6DD580AA}"/>
     <hyperlink ref="B14" r:id="rId25" xr:uid="{149FD85D-6BAC-4E79-965A-4E1DB371554D}"/>
     <hyperlink ref="B36" r:id="rId26" xr:uid="{85A892E7-4CC8-416A-B056-F80EE05A2D41}"/>
     <hyperlink ref="B16" r:id="rId27" xr:uid="{B75FED28-B2A5-4AA7-BB1A-A29CA62218B9}"/>
+    <hyperlink ref="B25" r:id="rId28" xr:uid="{7FB43CD6-FEE7-4005-B6B4-A4C607F8D458}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2449,7 +2483,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E47D55AA-24E1-48BD-B118-4FFFED8D4060}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.5546875" customWidth="1"/>
@@ -2477,15 +2511,15 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>39</v>
@@ -2502,66 +2536,66 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>159</v>
-      </c>
-      <c r="E4" t="s">
-        <v>158</v>
+        <v>49</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="B5" s="10" t="s">
+      <c r="A5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="E5" s="5">
+      <c r="D6" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="E6" s="5">
         <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>160</v>
-      </c>
-      <c r="E6" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>4</v>
+        <v>157</v>
+      </c>
+      <c r="E7" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>151</v>
+        <v>52</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
-        <v>139</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>152</v>
+        <v>6</v>
       </c>
       <c r="E8">
         <v>4</v>
@@ -2569,16 +2603,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>149</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="D9" t="s">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="E9">
         <v>4</v>
@@ -2586,10 +2620,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
       </c>
       <c r="D10" t="s">
         <v>6</v>
@@ -2600,37 +2637,36 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>161</v>
-      </c>
-      <c r="E11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="E12" s="5">
-        <v>3</v>
+      <c r="E12" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>32</v>
+        <v>138</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>144</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5" t="s">
-        <v>33</v>
+        <v>143</v>
       </c>
       <c r="E13" s="5">
         <v>3</v>
@@ -2638,56 +2674,72 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>44</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="C14" s="5"/>
       <c r="D14" s="5" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E14" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>162</v>
-      </c>
-      <c r="E15" t="s">
-        <v>158</v>
+      <c r="A15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>159</v>
+      </c>
+      <c r="E16" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C17" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="D17" t="s">
         <v>56</v>
       </c>
-      <c r="D16" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16">
+      <c r="E17">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{74592461-ECB0-4B8D-ADD2-990A8287FC80}"/>
-    <hyperlink ref="B8" r:id="rId2" xr:uid="{AE56E8A3-6574-4E6B-B527-C389062FFD5F}"/>
-    <hyperlink ref="B10" r:id="rId3" xr:uid="{95DC152E-AFF6-4E14-9FC8-D4457BF39508}"/>
-    <hyperlink ref="B9" r:id="rId4" xr:uid="{BEC94B9C-7E51-4B59-A597-F4F3FFE535B4}"/>
-    <hyperlink ref="B16" r:id="rId5" xr:uid="{FE1E462D-1567-4115-901B-5355F3B6C74D}"/>
-    <hyperlink ref="B12" r:id="rId6" xr:uid="{1679D661-FBFE-497E-9C50-301AAF57BCA4}"/>
-    <hyperlink ref="B5" r:id="rId7" xr:uid="{A773D842-D985-4CC7-A96C-ECE986F688CC}"/>
+    <hyperlink ref="B8" r:id="rId1" xr:uid="{74592461-ECB0-4B8D-ADD2-990A8287FC80}"/>
+    <hyperlink ref="B9" r:id="rId2" xr:uid="{AE56E8A3-6574-4E6B-B527-C389062FFD5F}"/>
+    <hyperlink ref="B11" r:id="rId3" xr:uid="{95DC152E-AFF6-4E14-9FC8-D4457BF39508}"/>
+    <hyperlink ref="B10" r:id="rId4" xr:uid="{BEC94B9C-7E51-4B59-A597-F4F3FFE535B4}"/>
+    <hyperlink ref="B17" r:id="rId5" xr:uid="{FE1E462D-1567-4115-901B-5355F3B6C74D}"/>
+    <hyperlink ref="B13" r:id="rId6" xr:uid="{1679D661-FBFE-497E-9C50-301AAF57BCA4}"/>
+    <hyperlink ref="B6" r:id="rId7" xr:uid="{A773D842-D985-4CC7-A96C-ECE986F688CC}"/>
+    <hyperlink ref="B4" r:id="rId8" xr:uid="{FBA813CA-47BA-4C2D-AE7F-8C81302C372A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2723,14 +2775,14 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E2" s="8">
         <v>6</v>
@@ -2738,14 +2790,14 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E3" s="8">
         <v>6</v>
@@ -2753,16 +2805,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>147</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>149</v>
       </c>
       <c r="E4" s="8">
         <v>6</v>
@@ -2770,14 +2822,14 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E5" s="8">
         <v>6</v>
@@ -2785,14 +2837,14 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E6" s="8">
         <v>6</v>
@@ -2800,14 +2852,14 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E7" s="8">
         <v>6</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\TaikoNavigation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD0CC25-7DC5-4067-A59E-0066665B5E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7CEDC2F-B8E1-4A7B-83BE-20C57AA91078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3684" yWindow="4812" windowWidth="25476" windowHeight="13560" activeTab="1" xr2:uid="{21938866-CF94-43A1-8F72-DCC95449F496}"/>
+    <workbookView xWindow="1536" yWindow="2064" windowWidth="25476" windowHeight="13560" xr2:uid="{21938866-CF94-43A1-8F72-DCC95449F496}"/>
   </bookViews>
   <sheets>
     <sheet name="主页" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="184">
   <si>
     <t>name</t>
   </si>
@@ -45,572 +45,644 @@
     <t>0.png</t>
   </si>
   <si>
+    <t>https://space.bilibili.com/332563726</t>
+  </si>
+  <si>
+    <t>wec.png</t>
+  </si>
+  <si>
+    <t>日本玩家搭建的wiki，数据全面历史悠久</t>
+  </si>
+  <si>
+    <t>wiki.png</t>
+  </si>
+  <si>
+    <t>韩国玩家搭建的wiki，数据全面历史悠久</t>
+  </si>
+  <si>
+    <t>wiki_ko.png</t>
+  </si>
+  <si>
+    <t>https://taiko.fandom.com/zh/wiki/%E9%A6%96%E9%A0%81</t>
+  </si>
+  <si>
+    <t>音游地图</t>
+  </si>
+  <si>
+    <t>https://map.bemanicn.com/games/31</t>
+  </si>
+  <si>
+    <t>bemani.png</t>
+  </si>
+  <si>
+    <t>https://qun.qq.com/universal-share/share?ac=1&amp;authKey=IT7nCJLnewnitCHF61dxFUr2oVgR%2F6L0Chf7hIVAbh2sds16Br9%2B9CJssWnQiJO%2B&amp;busi_data=eyJncm91cENvZGUiOiIyOTAxODQxNDciLCJ0b2tlbiI6InJ3aHBJV1dLT0VYeHZjejVDRTllUFNpbTd3WHFYaWxGa1FMMzR4QWl4U3I4ZTVva21jRms5UnhUSzErRVhaSTgiLCJ1aW4iOiIzMzkyOTA2NDAifQ%3D%3D&amp;data=yDKLKd-Pa1L25EwAck6iQn-SH2deyWEvvRAbjzZj91vQaobsQJsvUMI8ADHoc7F2LbTNINM7_16YNwHgkWoNJg&amp;svctype=4&amp;tempid=h5_group_info</t>
+  </si>
+  <si>
+    <t>https://hatukiyura.sakura.ne.jp/</t>
+  </si>
+  <si>
+    <t>叶月由罗的个人主页，可以查询到其往年作品和活动日程</t>
+  </si>
+  <si>
+    <t>https://prober.ourtaiko.org/search</t>
+  </si>
+  <si>
+    <t>luluxia.png</t>
+  </si>
+  <si>
+    <t>https://hatahata.outsystemscloud.com/DonderNote/Menu</t>
+  </si>
+  <si>
+    <t>DonderNote.png</t>
+  </si>
+  <si>
+    <t>OpenTaiko</t>
+  </si>
+  <si>
+    <t>https://opentaiko.github.io/</t>
+  </si>
+  <si>
+    <t>OpenTaiko.ico</t>
+  </si>
+  <si>
+    <t>ESE TJA</t>
+  </si>
+  <si>
+    <t>https://ese.tjadataba.se/ESE/ESE/</t>
+  </si>
+  <si>
+    <t>ese.png</t>
+  </si>
+  <si>
+    <t>https://wwaya.lanzoup.com/iHj8b3e7ooyh</t>
+  </si>
+  <si>
+    <t>可视化的谱面编辑，让小白也能迅速创建自己的太鼓谱面</t>
+  </si>
+  <si>
+    <t>PeepoDrumKit.ico</t>
+  </si>
+  <si>
+    <t>TaikoWeb</t>
+  </si>
+  <si>
+    <t>https://taiko.asia/</t>
+  </si>
+  <si>
+    <t>太鼓达人在线模拟器</t>
+  </si>
+  <si>
+    <t>taikoweb.png</t>
+  </si>
+  <si>
+    <t>https://olaf5103.cn:765/taiko/songs</t>
+  </si>
+  <si>
+    <t>Donder Asistant</t>
+  </si>
+  <si>
+    <t>Tja-Tools</t>
+  </si>
+  <si>
+    <t>Tja Analyser</t>
+  </si>
+  <si>
+    <t>TaikoImager</t>
+  </si>
+  <si>
+    <t>kokoko.jpg</t>
+  </si>
+  <si>
+    <t>菌菌控制台</t>
+  </si>
+  <si>
+    <t>https://kinoko.zorua.cn/</t>
+  </si>
+  <si>
+    <t>菌菌控制台！可以管理自己的成绩以及使用菌菌的多项隐藏功能！</t>
+  </si>
+  <si>
+    <t>junjun.png</t>
+  </si>
+  <si>
+    <t>菌菌别名表格</t>
+  </si>
+  <si>
+    <t>https://www.kdocs.cn/l/cauSVZId2ohu</t>
+  </si>
+  <si>
+    <t>Sakura Bot</t>
+  </si>
+  <si>
+    <t>https://viewer.sakura-bot.cn/</t>
+  </si>
+  <si>
+    <t>猫鼓的小店</t>
+  </si>
+  <si>
+    <t>cat.png</t>
+  </si>
+  <si>
+    <t>power.png</t>
+  </si>
+  <si>
+    <t>sakataiko.png</t>
+  </si>
+  <si>
+    <t>stg.png</t>
+  </si>
+  <si>
+    <t>伪都特产私棍</t>
+  </si>
+  <si>
+    <t>otto.png</t>
+  </si>
+  <si>
+    <t>单手全连逆战</t>
+  </si>
+  <si>
+    <t>nizhan.png</t>
+  </si>
+  <si>
+    <t>狂澜怒涛</t>
+  </si>
+  <si>
+    <t>7f7f.png</t>
+  </si>
+  <si>
+    <t>watermelon.png</t>
+  </si>
+  <si>
+    <t>ZDR</t>
+  </si>
+  <si>
+    <t>zdr.png</t>
+  </si>
+  <si>
+    <t>活体搁浅</t>
+  </si>
+  <si>
+    <t>wai.jpg</t>
+  </si>
+  <si>
+    <t>deng.png</t>
+  </si>
+  <si>
+    <t>小言罐头</t>
+  </si>
+  <si>
+    <t>yan.png</t>
+  </si>
+  <si>
+    <t>yuan.png</t>
+  </si>
+  <si>
+    <t>小章木工坊</t>
+  </si>
+  <si>
+    <t>https://mobile.yangkeduo.com/mall_page.html?ps=IpGOWhdEwr</t>
+  </si>
+  <si>
+    <t>pdd.png</t>
+  </si>
+  <si>
+    <t>铭盛科技</t>
+  </si>
+  <si>
+    <t>mingsheng.png</t>
+  </si>
+  <si>
+    <t>太鼓之达人官方</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>太鼓之达人官方Bilibili账号</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>华立电竞官方Bilibili账号</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>太鼓Fandom</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>全国玩家群</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>全国范围的2000人玩家交流群</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>太鼓WIKI 日</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>太鼓WIKI 韩</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PeepoDrumKit</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Database定数</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>华立官方淘汰的次品官机配件，可以尝试抽奖</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>20元以内性价比首选，建议选圆头枫木，自己购置手胶</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://imager.donders.work</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://rating.haxif.com</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI Rating分析</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>让AI对你的成绩信息进行分析总结</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>stv.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>控制器调试辅助</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>StevenXMH</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>kokoko.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://wiki.ourtaiko.org/songs</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OurtaikoWiki</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>国内玩家开发的成绩评分系统及谱面查询</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>可可子</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://kkz.haxif.com/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://shop525820965.taobao.com/category.htm?spm=pc_detail.30350276.shop_block.dshopinfo.56be7dd6dsI5yg&amp;topIds=719510077825</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Power的小店</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://shop104239116.taobao.com/category.htm?spm=pc_detail.30350276.shop_block.dshopinfo.6d1c6252j87z2N&amp;topIds=1050934996989</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.bought.0.0.5228252dPRFudb&amp;userId=3698605461</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.bought.0.0.5228252dPRFudb&amp;userId=1107549877</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>神童同学</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.27bd42b3JlfOmI&amp;userId=2709663921</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.6ad31a5as9AFCH&amp;userId=2213174146625</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>西瓜的音游小铺</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.12cf163dmL6Yrg&amp;userId=2135576311</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.46e4b2f2l91x1H&amp;userId=674644841</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://shop109402001.taobao.com/category.htm?spm=pc_detail.30350276.shop_block.dshopinfo.32217dd6Wwfp8W&amp;topIds=567063533860</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.52ca49fauX932Z&amp;userId=3704968269</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.19c73350BIZScL&amp;userId=3887875950</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>不灭的灯</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>哈基缘</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.150a505eFDpfwo&amp;userId=45429781</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.7dc67a0caZ3ysg&amp;userId=2200623233408</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.5b1052c7F1Fyox&amp;userId=2215320654516</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://e.tb.cn/h.8XcgB01nntTZ3dL?tk=AyHygHkEYP4</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://video.donders.work</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TaikoNauts</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tjaanalyzer-ja.ckq.me</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://whmhammer.github.io/tja-tools</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://stevetaikocon.stevexmh.net</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tjapre.haxif.com</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TaikoNauts.ico</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://taikonauts-docs.pages.dev</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.79bc2456WMXQuw&amp;userId=1814109102</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>napZ</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>za.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZA鼓以及各种太鼓配件</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TJA2Video</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TJA2Video.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://fanmade.ourtaiko.org/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OurTaikoFanmade</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>制谱器</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>linetitle</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>自制谱社区</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>谱面预览生成</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>模拟器</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>crt.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>fandom.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>oLaf.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>sakura.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OurTaiko.ico</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://dafrok.github.io/donder-assistant/constants</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>主营猫鼓、猫棍（榉木）</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>主营大力鼓、夯棍</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OurTaiko自制谱社区，可以在这里分享和体验太鼓自制谱</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>为歌曲添加别名用于菌菌的歌曲查询</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://yuradan.evattri.win/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>葉月ゆら段位道場</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>yura.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>葉月ゆら段位自制谱征集中</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TaikoImager</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以获得还原官方视觉效果的谱面片段或谱面图，支持各种演奏选项；支持以小节为单位裁切谱面并拼接，生成带有对应音频的练习谱；还有生成歌曲名牌和TNDE的音符皮肤等功能</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>将tja文件渲染为视频，便于分享，支持多难度同时渲染</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以将tja文件转化为wiki样式的静态谱面图</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>华立电竞</t>
-  </si>
-  <si>
-    <t>https://space.bilibili.com/332563726</t>
-  </si>
-  <si>
-    <t>wec.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>https://wikiwiki.jp/taiko-fumen/</t>
-  </si>
-  <si>
-    <t>日本玩家搭建的wiki，数据全面历史悠久</t>
-  </si>
-  <si>
-    <t>wiki.png</t>
-  </si>
-  <si>
-    <t>韩国玩家搭建的wiki，数据全面历史悠久</t>
-  </si>
-  <si>
-    <t>wiki_ko.png</t>
-  </si>
-  <si>
-    <t>https://taiko.fandom.com/zh/wiki/%E9%A6%96%E9%A0%81</t>
-  </si>
-  <si>
-    <t>音游地图</t>
-  </si>
-  <si>
-    <t>https://map.bemanicn.com/games/31</t>
-  </si>
-  <si>
-    <t>bemani.png</t>
-  </si>
-  <si>
-    <t>https://qun.qq.com/universal-share/share?ac=1&amp;authKey=IT7nCJLnewnitCHF61dxFUr2oVgR%2F6L0Chf7hIVAbh2sds16Br9%2B9CJssWnQiJO%2B&amp;busi_data=eyJncm91cENvZGUiOiIyOTAxODQxNDciLCJ0b2tlbiI6InJ3aHBJV1dLT0VYeHZjejVDRTllUFNpbTd3WHFYaWxGa1FMMzR4QWl4U3I4ZTVva21jRms5UnhUSzErRVhaSTgiLCJ1aW4iOiIzMzkyOTA2NDAifQ%3D%3D&amp;data=yDKLKd-Pa1L25EwAck6iQn-SH2deyWEvvRAbjzZj91vQaobsQJsvUMI8ADHoc7F2LbTNINM7_16YNwHgkWoNJg&amp;svctype=4&amp;tempid=h5_group_info</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://taiko.wiki/?lang=zh-cn</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>葉月ゆら主页</t>
-  </si>
-  <si>
-    <t>https://hatukiyura.sakura.ne.jp/</t>
-  </si>
-  <si>
-    <t>叶月由罗的个人主页，可以查询到其往年作品和活动日程</t>
-  </si>
-  <si>
-    <t>yura.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tja Analyser</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>由BEMANICN为了方便街机玩家出勤，而建立的查询国内街机的小工具。
+在使用本工具此查找街机的同时，也请您一起协助完善店铺信息，让更多的玩家受益。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://kinoko.zorua.cn/arcades</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>太鼓地图 Revival</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>junjun.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>https://fumen-database.com/difficulty/?const_desc</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>fumen-database建立的虹版谱面定数系统，用于总结谱面的综合打分难度</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>手动记录成绩信息的工具，总结了日本玩家编篡的全良难度表</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>本维基是关于太鼓之达人和相关的东西，任何人也可以来修改的啊，咚！</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Donder查分器</t>
-  </si>
-  <si>
-    <t>https://prober.ourtaiko.org/search</t>
-  </si>
-  <si>
-    <t>luluxia.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>DonderNote</t>
-  </si>
-  <si>
-    <t>https://hatahata.outsystemscloud.com/DonderNote/Menu</t>
-  </si>
-  <si>
-    <t>DonderNote.png</t>
-  </si>
-  <si>
-    <t>OpenTaiko</t>
-  </si>
-  <si>
-    <t>https://opentaiko.github.io/</t>
-  </si>
-  <si>
-    <t>OpenTaiko.ico</t>
-  </si>
-  <si>
-    <t>ESE TJA</t>
-  </si>
-  <si>
-    <t>https://ese.tjadataba.se/ESE/ESE/</t>
-  </si>
-  <si>
-    <t>ese.png</t>
-  </si>
-  <si>
-    <t>ESE Helper</t>
-  </si>
-  <si>
-    <t>https://taiko.vanillaaaa.org/</t>
-  </si>
-  <si>
-    <t>https://wwaya.lanzoup.com/iHj8b3e7ooyh</t>
-  </si>
-  <si>
-    <t>可视化的谱面编辑，让小白也能迅速创建自己的太鼓谱面</t>
-  </si>
-  <si>
-    <t>PeepoDrumKit.ico</t>
-  </si>
-  <si>
-    <t>TaikoWeb</t>
-  </si>
-  <si>
-    <t>https://taiko.asia/</t>
-  </si>
-  <si>
-    <t>太鼓达人在线模拟器</t>
-  </si>
-  <si>
-    <t>taikoweb.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家维护的官方谱面库，数量大，但时常和官谱出现出入</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tja-Tools</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>想说找一些指定范围内的BPM歌曲来针对锻炼读谱和手速, 但由于BPM的定义范围可能略有模糊和微妙。
+那就由黑猫突发奇想自己来定义并设计这么一套可搜索BPM和流速的太鼓的国行歌曲搜索系统吧!</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>歌曲检索器</t>
-  </si>
-  <si>
-    <t>https://olaf5103.cn:765/taiko/songs</t>
-  </si>
-  <si>
-    <t>Donder Asistant</t>
-  </si>
-  <si>
-    <t>Tja-Tools</t>
-  </si>
-  <si>
-    <t>可以将tja文件转化为静态谱面图</t>
-  </si>
-  <si>
-    <t>Tja Analyser</t>
-  </si>
-  <si>
-    <t>TaikoImager</t>
-  </si>
-  <si>
-    <t>可以获得还原官方视觉效果的谱面片段或谱面图，支持各种演奏选项</t>
-  </si>
-  <si>
-    <t>AI定数预测</t>
-  </si>
-  <si>
-    <t>让AI对你创作的谱面进行难度的初步评估</t>
-  </si>
-  <si>
-    <t>kokoko.jpg</t>
-  </si>
-  <si>
-    <t>菌菌控制台</t>
-  </si>
-  <si>
-    <t>https://kinoko.zorua.cn/</t>
-  </si>
-  <si>
-    <t>菌菌控制台！可以管理自己的成绩以及使用菌菌的多项隐藏功能！</t>
-  </si>
-  <si>
-    <t>junjun.png</t>
-  </si>
-  <si>
-    <t>菌菌别名表格</t>
-  </si>
-  <si>
-    <t>https://www.kdocs.cn/l/cauSVZId2ohu</t>
-  </si>
-  <si>
-    <t>Sakura Bot</t>
-  </si>
-  <si>
-    <t>https://viewer.sakura-bot.cn/</t>
-  </si>
-  <si>
-    <t>猫鼓的小店</t>
-  </si>
-  <si>
-    <t>cat.png</t>
-  </si>
-  <si>
-    <t>power.png</t>
-  </si>
-  <si>
-    <t>sakataiko.png</t>
-  </si>
-  <si>
-    <t>stg.png</t>
-  </si>
-  <si>
-    <t>伪都特产私棍</t>
-  </si>
-  <si>
-    <t>otto.png</t>
-  </si>
-  <si>
-    <t>单手全连逆战</t>
-  </si>
-  <si>
-    <t>nizhan.png</t>
-  </si>
-  <si>
-    <t>狂澜怒涛</t>
-  </si>
-  <si>
-    <t>7f7f.png</t>
-  </si>
-  <si>
-    <t>watermelon.png</t>
-  </si>
-  <si>
-    <t>ZDR</t>
-  </si>
-  <si>
-    <t>zdr.png</t>
-  </si>
-  <si>
-    <t>活体搁浅</t>
-  </si>
-  <si>
-    <t>wai.jpg</t>
-  </si>
-  <si>
-    <t>deng.png</t>
-  </si>
-  <si>
-    <t>小言罐头</t>
-  </si>
-  <si>
-    <t>yan.png</t>
-  </si>
-  <si>
-    <t>yuan.png</t>
-  </si>
-  <si>
-    <t>小章木工坊</t>
-  </si>
-  <si>
-    <t>https://mobile.yangkeduo.com/mall_page.html?ps=IpGOWhdEwr</t>
-  </si>
-  <si>
-    <t>pdd.png</t>
-  </si>
-  <si>
-    <t>铭盛科技</t>
-  </si>
-  <si>
-    <t>mingsheng.png</t>
-  </si>
-  <si>
-    <t>太鼓之达人官方</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>太鼓之达人官方Bilibili账号</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>华立电竞官方Bilibili账号</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>太鼓Fandom</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>全国玩家群</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>全国范围的2000人玩家交流群</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>太鼓WIKI 日</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>太鼓WIKI 韩</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>PeepoDrumKit</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Database定数</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>华立官方淘汰的次品官机配件，可以尝试抽奖</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>20元以内性价比首选，建议选圆头枫木，自己购置手胶</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://imager.donders.work</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://rating.haxif.com</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>AI Rating分析</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>让AI对你的成绩信息进行分析总结</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>stv.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>控制器调试辅助</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>StevenXMH</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>kokoko.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://wiki.ourtaiko.org/songs</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>OurtaikoWiki</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>国内玩家开发的成绩评分系统及谱面查询</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>可可子</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://kkz.haxif.com/</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://shop525820965.taobao.com/category.htm?spm=pc_detail.30350276.shop_block.dshopinfo.56be7dd6dsI5yg&amp;topIds=719510077825</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Power的小店</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://shop104239116.taobao.com/category.htm?spm=pc_detail.30350276.shop_block.dshopinfo.6d1c6252j87z2N&amp;topIds=1050934996989</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>鱼鼓的小店</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.goofish.com/personal?spm=a21ybx.bought.0.0.5228252dPRFudb&amp;userId=3698605461</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.goofish.com/personal?spm=a21ybx.bought.0.0.5228252dPRFudb&amp;userId=1107549877</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>神童同学</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.27bd42b3JlfOmI&amp;userId=2709663921</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.6ad31a5as9AFCH&amp;userId=2213174146625</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>西瓜的音游小铺</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.12cf163dmL6Yrg&amp;userId=2135576311</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.46e4b2f2l91x1H&amp;userId=674644841</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://shop109402001.taobao.com/category.htm?spm=pc_detail.30350276.shop_block.dshopinfo.32217dd6Wwfp8W&amp;topIds=567063533860</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.52ca49fauX932Z&amp;userId=3704968269</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.19c73350BIZScL&amp;userId=3887875950</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>不灭的灯</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>哈基缘</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.150a505eFDpfwo&amp;userId=45429781</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.7dc67a0caZ3ysg&amp;userId=2200623233408</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.5b1052c7F1Fyox&amp;userId=2215320654516</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://e.tb.cn/h.8XcgB01nntTZ3dL?tk=AyHygHkEYP4</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://video.donders.work</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>将tja文件渲染为视频，便于分享</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>TaikoNauts</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tjaanalyzer-ja.ckq.me</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://whmhammer.github.io/tja-tools</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://stevetaikocon.stevexmh.net</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tjapre.haxif.com</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>TaikoNauts.ico</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://taikonauts-docs.pages.dev</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.goofish.com/personal?spm=a21ybx.item.itemHeader.1.79bc2456WMXQuw&amp;userId=1814109102</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>napZ</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>za.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ZA鼓以及各种太鼓配件</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>TJA2Video</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>TJA2Video.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://fanmade.ourtaiko.org/</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>OurTaikoFanmade</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>中国自制谱社区</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>制谱器</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>linetitle</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>自制谱社区</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>谱面预览生成</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>模拟器</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>其他</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>crt.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>fandom.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>oLaf.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>sakura.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>OurTaiko.ico</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://dafrok.github.io/donder-assistant/constants</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>主营猫鼓、猫棍（榉木）</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>主营大力鼓、夯棍</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>OurTaiko自制谱社区，可以在这里分享和体验太鼓自制谱</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>为歌曲添加别名用于菌菌的歌曲查询</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>上传 TJA、粘贴文本，或选择示例谱面，在浏览器内完成定数预测</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>谱面定数 AI 预测</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>POLYMONOP</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1227,7 +1299,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1260,6 +1332,18 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="35" borderId="0" xfId="42" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="42" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1644,7 +1728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2205B9E-1FE6-4EB7-B604-2CFC0207A242}">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.5546875" customWidth="1"/>
@@ -1672,13 +1756,13 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>6</v>
@@ -1689,16 +1773,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="E3" s="2">
         <v>1</v>
@@ -1706,16 +1790,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="E4" s="2">
         <v>1</v>
@@ -1723,16 +1807,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>83</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>163</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
@@ -1740,29 +1824,33 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>173</v>
+      </c>
       <c r="D6" s="2" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="E7" s="2">
         <v>1</v>
@@ -1770,16 +1858,14 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>95</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="C8" s="12"/>
       <c r="D8" s="2" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="E8" s="2">
         <v>1</v>
@@ -1787,48 +1873,50 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E9" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E10" s="3">
-        <v>2</v>
+      <c r="B10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="3"/>
+        <v>97</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="D11" s="3" t="s">
-        <v>12</v>
+        <v>147</v>
       </c>
       <c r="E11" s="3">
         <v>2</v>
@@ -1836,14 +1924,16 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="3"/>
+        <v>85</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="D12" s="3" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E12" s="3">
         <v>2</v>
@@ -1851,44 +1941,46 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>28</v>
+        <v>174</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E13" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="E14" s="5">
-        <v>3</v>
+      <c r="A14" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>32</v>
+        <v>122</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>128</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5" t="s">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="E15" s="5">
         <v>3</v>
@@ -1896,16 +1988,14 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>168</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="5"/>
       <c r="D16" s="5" t="s">
-        <v>164</v>
+        <v>26</v>
       </c>
       <c r="E16" s="5">
         <v>3</v>
@@ -1913,16 +2003,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>39</v>
+        <v>136</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>135</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>40</v>
+        <v>151</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="E17" s="5">
         <v>3</v>
@@ -1930,16 +2020,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E18" s="5">
         <v>3</v>
@@ -1947,12 +2037,14 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="5"/>
       <c r="D19" s="5" t="s">
         <v>36</v>
       </c>
@@ -1962,48 +2054,50 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="5"/>
+        <v>28</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>176</v>
+      </c>
       <c r="D20" s="5" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E20" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C21" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21">
-        <v>4</v>
+      <c r="A21" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E21" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="D22" t="s">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="E22">
         <v>4</v>
@@ -2011,16 +2105,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>133</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>159</v>
       </c>
       <c r="D23" t="s">
-        <v>6</v>
+        <v>134</v>
       </c>
       <c r="E23">
         <v>4</v>
@@ -2028,13 +2122,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>177</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D24" t="s">
-        <v>6</v>
+        <v>124</v>
+      </c>
+      <c r="C24" t="s">
+        <v>160</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>178</v>
       </c>
       <c r="E24">
         <v>4</v>
@@ -2042,13 +2139,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>165</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>165</v>
+        <v>123</v>
       </c>
       <c r="D25" t="s">
-        <v>6</v>
+        <v>178</v>
       </c>
       <c r="E25">
         <v>4</v>
@@ -2056,27 +2153,30 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" t="s">
-        <v>47</v>
+        <v>38</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="D26" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="E26">
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>107</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>141</v>
+        <v>180</v>
+      </c>
+      <c r="B27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>179</v>
       </c>
       <c r="D27" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="E27">
         <v>4</v>
@@ -2084,16 +2184,13 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C28" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="D28" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="E28">
         <v>4</v>
@@ -2101,50 +2198,50 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>142</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="D29" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="E29">
         <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E30" s="6">
-        <v>5</v>
+      <c r="A30" t="s">
+        <v>182</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C30" t="s">
+        <v>181</v>
+      </c>
+      <c r="D30" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30">
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C31" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" s="6" t="s">
         <v>169</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>60</v>
       </c>
       <c r="E31" s="6">
         <v>5</v>
@@ -2152,14 +2249,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" s="6"/>
+        <v>48</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>152</v>
+      </c>
       <c r="D32" s="6" t="s">
-        <v>163</v>
+        <v>46</v>
       </c>
       <c r="E32" s="6">
         <v>5</v>
@@ -2167,48 +2266,46 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>114</v>
+        <v>49</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="6" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="E33" s="6">
         <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E34" s="8">
-        <v>6</v>
+      <c r="A34" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E34" s="6">
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="E35" s="8">
         <v>6</v>
@@ -2216,16 +2313,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>147</v>
+        <v>53</v>
       </c>
       <c r="E36" s="8">
         <v>6</v>
@@ -2233,14 +2330,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C37" s="8"/>
+        <v>129</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>132</v>
+      </c>
       <c r="D37" s="8" t="s">
-        <v>68</v>
+        <v>131</v>
       </c>
       <c r="E37" s="8">
         <v>6</v>
@@ -2248,14 +2347,14 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
-        <v>108</v>
+        <v>183</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8" t="s">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="E38" s="8">
         <v>6</v>
@@ -2263,14 +2362,14 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="E39" s="8">
         <v>6</v>
@@ -2278,14 +2377,14 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="E40" s="8">
         <v>6</v>
@@ -2293,14 +2392,14 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="E41" s="8">
         <v>6</v>
@@ -2308,14 +2407,14 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="E42" s="8">
         <v>6</v>
@@ -2323,14 +2422,14 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="E43" s="8">
         <v>6</v>
@@ -2338,14 +2437,14 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="E44" s="8">
         <v>6</v>
@@ -2353,14 +2452,14 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="8" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="E45" s="8">
         <v>6</v>
@@ -2368,14 +2467,14 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="8" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="E46" s="8">
         <v>6</v>
@@ -2383,14 +2482,14 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="8" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="E47" s="8">
         <v>6</v>
@@ -2398,14 +2497,14 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>131</v>
+        <v>68</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>133</v>
+        <v>104</v>
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="8" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="E48" s="8">
         <v>6</v>
@@ -2413,16 +2512,14 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>101</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C49" s="8"/>
       <c r="D49" s="8" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="E49" s="8">
         <v>6</v>
@@ -2430,52 +2527,74 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>135</v>
+        <v>71</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E50" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E51" s="8">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B21" r:id="rId1" xr:uid="{0814D534-9BBD-4FF2-91BF-D9D2FA195367}"/>
-    <hyperlink ref="B28" r:id="rId2" xr:uid="{1C29CD7D-8195-4F43-BF25-3937379C553D}"/>
-    <hyperlink ref="B27" r:id="rId3" xr:uid="{C7DC1DD1-A540-4732-A529-6E4F4FC7E8F3}"/>
-    <hyperlink ref="B38" r:id="rId4" xr:uid="{CACBC6E3-169E-4706-B683-51554D0D68AD}"/>
-    <hyperlink ref="B10" r:id="rId5" xr:uid="{E4702D2D-6FCD-4B5B-9E81-602FCFEC045E}"/>
-    <hyperlink ref="B33" r:id="rId6" xr:uid="{A1F7C2BA-EE73-4EAF-99B5-5E02AFC9E006}"/>
-    <hyperlink ref="B34" r:id="rId7" xr:uid="{AE381AE9-C7E3-48F7-BEC9-7DABD944D317}"/>
-    <hyperlink ref="B35" r:id="rId8" xr:uid="{FA0E93C8-8380-4554-B1AF-7A314C12F0F0}"/>
-    <hyperlink ref="B41" r:id="rId9" xr:uid="{95CEEF74-399F-4BB0-84CC-A80EC975FADE}"/>
-    <hyperlink ref="B47" r:id="rId10" xr:uid="{1243E3BB-84D1-4ACA-9021-EE8FCA8830B3}"/>
-    <hyperlink ref="B37" r:id="rId11" xr:uid="{B8B71B7B-0A03-4E4B-847B-71311DFEDCA0}"/>
-    <hyperlink ref="B44" r:id="rId12" xr:uid="{F77A6A42-7643-4489-98B0-ABE8B87CF767}"/>
-    <hyperlink ref="B43" r:id="rId13" xr:uid="{6B2D5271-7CC5-4F08-AB0C-B89338B4A63C}"/>
-    <hyperlink ref="B42" r:id="rId14" xr:uid="{6D333F99-D332-4EAB-BF65-094492050942}"/>
-    <hyperlink ref="B40" r:id="rId15" xr:uid="{C33A6450-F262-44B1-AFB0-3337948BF9A0}"/>
-    <hyperlink ref="B39" r:id="rId16" xr:uid="{B7F01162-C6EA-409F-B151-19867DBC753A}"/>
-    <hyperlink ref="B45" r:id="rId17" xr:uid="{B243319D-2D2D-4A67-B44E-198D616C4C29}"/>
-    <hyperlink ref="B46" r:id="rId18" xr:uid="{52F90D2B-5B0E-456F-9F77-3826408A3A90}"/>
-    <hyperlink ref="B48" r:id="rId19" xr:uid="{4A20EF09-9308-4377-92A2-06F8794335E9}"/>
-    <hyperlink ref="B50" r:id="rId20" xr:uid="{CB8B7E6A-16D0-4487-95BC-BBCDB1DDB762}"/>
-    <hyperlink ref="B22" r:id="rId21" xr:uid="{2AA1A8B2-65B5-4DFD-AE88-E03CD884F638}"/>
-    <hyperlink ref="B24" r:id="rId22" xr:uid="{7CFFC6E2-2149-496D-87C9-33DB97F87074}"/>
-    <hyperlink ref="B23" r:id="rId23" xr:uid="{4389E72A-7A4A-4C46-9BB9-695300B8D532}"/>
-    <hyperlink ref="B29" r:id="rId24" xr:uid="{3C38A248-15F8-4BCA-BE67-A17C6DD580AA}"/>
-    <hyperlink ref="B14" r:id="rId25" xr:uid="{149FD85D-6BAC-4E79-965A-4E1DB371554D}"/>
-    <hyperlink ref="B36" r:id="rId26" xr:uid="{85A892E7-4CC8-416A-B056-F80EE05A2D41}"/>
-    <hyperlink ref="B16" r:id="rId27" xr:uid="{B75FED28-B2A5-4AA7-BB1A-A29CA62218B9}"/>
-    <hyperlink ref="B25" r:id="rId28" xr:uid="{7FB43CD6-FEE7-4005-B6B4-A4C607F8D458}"/>
+    <hyperlink ref="B22" r:id="rId1" xr:uid="{0814D534-9BBD-4FF2-91BF-D9D2FA195367}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{1C29CD7D-8195-4F43-BF25-3937379C553D}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{C7DC1DD1-A540-4732-A529-6E4F4FC7E8F3}"/>
+    <hyperlink ref="B39" r:id="rId4" xr:uid="{CACBC6E3-169E-4706-B683-51554D0D68AD}"/>
+    <hyperlink ref="B11" r:id="rId5" xr:uid="{E4702D2D-6FCD-4B5B-9E81-602FCFEC045E}"/>
+    <hyperlink ref="B34" r:id="rId6" xr:uid="{A1F7C2BA-EE73-4EAF-99B5-5E02AFC9E006}"/>
+    <hyperlink ref="B35" r:id="rId7" xr:uid="{AE381AE9-C7E3-48F7-BEC9-7DABD944D317}"/>
+    <hyperlink ref="B36" r:id="rId8" xr:uid="{FA0E93C8-8380-4554-B1AF-7A314C12F0F0}"/>
+    <hyperlink ref="B42" r:id="rId9" xr:uid="{95CEEF74-399F-4BB0-84CC-A80EC975FADE}"/>
+    <hyperlink ref="B48" r:id="rId10" xr:uid="{1243E3BB-84D1-4ACA-9021-EE8FCA8830B3}"/>
+    <hyperlink ref="B38" r:id="rId11" xr:uid="{B8B71B7B-0A03-4E4B-847B-71311DFEDCA0}"/>
+    <hyperlink ref="B45" r:id="rId12" xr:uid="{F77A6A42-7643-4489-98B0-ABE8B87CF767}"/>
+    <hyperlink ref="B44" r:id="rId13" xr:uid="{6B2D5271-7CC5-4F08-AB0C-B89338B4A63C}"/>
+    <hyperlink ref="B43" r:id="rId14" xr:uid="{6D333F99-D332-4EAB-BF65-094492050942}"/>
+    <hyperlink ref="B41" r:id="rId15" xr:uid="{C33A6450-F262-44B1-AFB0-3337948BF9A0}"/>
+    <hyperlink ref="B40" r:id="rId16" xr:uid="{B7F01162-C6EA-409F-B151-19867DBC753A}"/>
+    <hyperlink ref="B46" r:id="rId17" xr:uid="{B243319D-2D2D-4A67-B44E-198D616C4C29}"/>
+    <hyperlink ref="B47" r:id="rId18" xr:uid="{52F90D2B-5B0E-456F-9F77-3826408A3A90}"/>
+    <hyperlink ref="B49" r:id="rId19" xr:uid="{4A20EF09-9308-4377-92A2-06F8794335E9}"/>
+    <hyperlink ref="B51" r:id="rId20" xr:uid="{CB8B7E6A-16D0-4487-95BC-BBCDB1DDB762}"/>
+    <hyperlink ref="B23" r:id="rId21" xr:uid="{2AA1A8B2-65B5-4DFD-AE88-E03CD884F638}"/>
+    <hyperlink ref="B25" r:id="rId22" xr:uid="{7CFFC6E2-2149-496D-87C9-33DB97F87074}"/>
+    <hyperlink ref="B24" r:id="rId23" xr:uid="{4389E72A-7A4A-4C46-9BB9-695300B8D532}"/>
+    <hyperlink ref="B30" r:id="rId24" xr:uid="{3C38A248-15F8-4BCA-BE67-A17C6DD580AA}"/>
+    <hyperlink ref="B15" r:id="rId25" xr:uid="{149FD85D-6BAC-4E79-965A-4E1DB371554D}"/>
+    <hyperlink ref="B37" r:id="rId26" xr:uid="{85A892E7-4CC8-416A-B056-F80EE05A2D41}"/>
+    <hyperlink ref="B17" r:id="rId27" xr:uid="{B75FED28-B2A5-4AA7-BB1A-A29CA62218B9}"/>
+    <hyperlink ref="B26" r:id="rId28" xr:uid="{7FB43CD6-FEE7-4005-B6B4-A4C607F8D458}"/>
+    <hyperlink ref="B21" r:id="rId29" xr:uid="{4DD1949B-BEB0-4C45-A420-40EDF792FEF5}"/>
+    <hyperlink ref="B4" r:id="rId30" xr:uid="{1B8B52B1-ACF2-42E2-814D-BAD9992C5EEB}"/>
+    <hyperlink ref="B5" r:id="rId31" xr:uid="{D7D78A78-7F5D-43E7-A139-9B58270825AA}"/>
+    <hyperlink ref="B8" r:id="rId32" xr:uid="{DC0688C0-A34A-471E-A0BD-26669AD919AF}"/>
+    <hyperlink ref="B12" r:id="rId33" xr:uid="{D3C9CA4B-0443-416F-8CF6-AD59AC5B709E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2483,398 +2602,191 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E47D55AA-24E1-48BD-B118-4FFFED8D4060}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.5546875" customWidth="1"/>
-    <col min="2" max="2" width="51.33203125" customWidth="1"/>
-    <col min="3" max="3" width="64.77734375" customWidth="1"/>
-    <col min="4" max="4" width="20.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" s="5"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B6" s="5"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="E2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="B7" s="5"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="5" t="s">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>156</v>
-      </c>
-      <c r="E5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="E6" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>157</v>
-      </c>
-      <c r="E7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>149</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C9" t="s">
-        <v>137</v>
-      </c>
-      <c r="D9" t="s">
-        <v>150</v>
-      </c>
-      <c r="E9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E12" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>141</v>
+      </c>
+      <c r="B13" t="s">
         <v>138</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="E13" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" s="5"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="5"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>159</v>
-      </c>
-      <c r="E16" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="5"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" t="s">
-        <v>56</v>
-      </c>
-      <c r="E17">
-        <v>4</v>
+      <c r="B17" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="B8" r:id="rId1" xr:uid="{74592461-ECB0-4B8D-ADD2-990A8287FC80}"/>
-    <hyperlink ref="B9" r:id="rId2" xr:uid="{AE56E8A3-6574-4E6B-B527-C389062FFD5F}"/>
-    <hyperlink ref="B11" r:id="rId3" xr:uid="{95DC152E-AFF6-4E14-9FC8-D4457BF39508}"/>
-    <hyperlink ref="B10" r:id="rId4" xr:uid="{BEC94B9C-7E51-4B59-A597-F4F3FFE535B4}"/>
-    <hyperlink ref="B17" r:id="rId5" xr:uid="{FE1E462D-1567-4115-901B-5355F3B6C74D}"/>
-    <hyperlink ref="B13" r:id="rId6" xr:uid="{1679D661-FBFE-497E-9C50-301AAF57BCA4}"/>
-    <hyperlink ref="B6" r:id="rId7" xr:uid="{A773D842-D985-4CC7-A96C-ECE986F688CC}"/>
-    <hyperlink ref="B4" r:id="rId8" xr:uid="{FBA813CA-47BA-4C2D-AE7F-8C81302C372A}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85318208-7F6B-460C-BEFD-B6FCAA294D89}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.5546875" customWidth="1"/>
-    <col min="2" max="2" width="51.33203125" customWidth="1"/>
-    <col min="3" max="3" width="64.77734375" customWidth="1"/>
-    <col min="4" max="4" width="20.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" s="8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="B2" s="8"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="E3" s="8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="B3" s="8"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="E4" s="8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+      <c r="B4" s="8"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" s="8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="B5" s="8"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="8"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="E6" s="8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="8">
-        <v>6</v>
-      </c>
+      <c r="B7" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" xr:uid="{B445E6B6-B847-495D-B6A5-26A68D515FFE}"/>
-    <hyperlink ref="B2" r:id="rId2" xr:uid="{BBEDAB73-3045-4443-84BB-B219DDB1E215}"/>
-    <hyperlink ref="B3" r:id="rId3" xr:uid="{A1BB8353-AEB9-4C7B-92F7-D0E822EDD0D8}"/>
-    <hyperlink ref="B5" r:id="rId4" xr:uid="{80BC0C96-4DBE-434F-9EB7-7FB33A501B50}"/>
-    <hyperlink ref="B7" r:id="rId5" xr:uid="{DE20E162-65FE-43C8-A3D5-3732E04DE2C2}"/>
-    <hyperlink ref="B4" r:id="rId6" xr:uid="{EDA0D7A9-D5C9-4E56-88F5-680DD9ED7DA6}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>